--- a/backend/prisma/seed-data/sales.xlsx
+++ b/backend/prisma/seed-data/sales.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ATI-User\Downloads\PCMI-Apps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder (2)\new-cms\backend\prisma\seed-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{441AE427-6258-49D9-82EC-49C38D69E607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{C49568A5-158C-924F-8878-5D75329F86B5}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="24885" windowHeight="14910"/>
   </bookViews>
   <sheets>
     <sheet name="Inv 10-Feb-26" sheetId="43" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inv 10-Feb-26'!$A$4:$AD$302</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="651">
   <si>
     <t>Account Receivable</t>
   </si>
@@ -1986,18 +1985,24 @@
   </si>
   <si>
     <t>Money Bucket Farewell Bu Henny</t>
+  </si>
+  <si>
+    <t>044/97/PCMI/AR/II/2026</t>
+  </si>
+  <si>
+    <t>Pengadaan untuk ANO Sumatera Forum 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -2236,23 +2241,23 @@
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -2275,11 +2280,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2312,7 +2317,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2326,14 +2331,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="15" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,77 +2346,77 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="14" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2427,12 +2432,12 @@
     <xf numFmtId="15" fontId="6" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2455,60 +2460,60 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Comma [0] 2" xfId="4" xr:uid="{E206625D-CE92-B946-878E-6AA0829E898C}"/>
-    <cellStyle name="Comma [0] 2 2" xfId="12" xr:uid="{2A804006-5001-5049-84D3-FB258FE2E1AB}"/>
-    <cellStyle name="Comma [0] 2 3" xfId="5" xr:uid="{20A799B3-BE5A-964F-BE1E-1391E29E7052}"/>
-    <cellStyle name="Comma [0] 2 3 2" xfId="10" xr:uid="{6B5DF09C-6668-004E-832C-859692394773}"/>
-    <cellStyle name="Comma [0] 2 3 2 2" xfId="17" xr:uid="{2EC272E1-F154-DE4D-8FFC-1738E0F2B485}"/>
-    <cellStyle name="Comma [0] 3" xfId="9" xr:uid="{DCC47050-EC02-4040-8ED8-306B64C985B1}"/>
-    <cellStyle name="Comma [0] 4" xfId="16" xr:uid="{5B145FB2-4D0A-B249-B369-54ABF0C38C9B}"/>
-    <cellStyle name="Comma 2" xfId="6" xr:uid="{EAAE8118-4A1E-3049-ADC2-FB2BB5557A52}"/>
-    <cellStyle name="Comma 2 2" xfId="7" xr:uid="{B0896BE0-35A1-2F49-8BC0-6D90093B48F4}"/>
-    <cellStyle name="Comma 3" xfId="13" xr:uid="{D01750FA-08E4-0C47-9357-0F62E9D605A3}"/>
-    <cellStyle name="Comma 4" xfId="15" xr:uid="{A2EC2101-5781-AC44-BED5-F1BDBB670F1A}"/>
+    <cellStyle name="Comma [0] 2" xfId="4"/>
+    <cellStyle name="Comma [0] 2 2" xfId="12"/>
+    <cellStyle name="Comma [0] 2 3" xfId="5"/>
+    <cellStyle name="Comma [0] 2 3 2" xfId="10"/>
+    <cellStyle name="Comma [0] 2 3 2 2" xfId="17"/>
+    <cellStyle name="Comma [0] 3" xfId="9"/>
+    <cellStyle name="Comma [0] 4" xfId="16"/>
+    <cellStyle name="Comma 2" xfId="6"/>
+    <cellStyle name="Comma 2 2" xfId="7"/>
+    <cellStyle name="Comma 3" xfId="13"/>
+    <cellStyle name="Comma 4" xfId="15"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{3B5401B9-DE75-EB48-9DE0-B2B7DAD183EC}"/>
-    <cellStyle name="Normal 2 2" xfId="8" xr:uid="{54DAEB53-87F6-084C-A87B-7176E7EB83C2}"/>
-    <cellStyle name="Normal 2 3" xfId="19" xr:uid="{FA86753D-0FFC-1948-8EF3-B2B2A5BEC3D7}"/>
-    <cellStyle name="Normal 3" xfId="14" xr:uid="{8B874317-EAD8-D042-9017-3A3DD28E4B28}"/>
-    <cellStyle name="Normal 3 4 2" xfId="11" xr:uid="{B424239B-ED7C-D142-AC4A-5D267E1997FC}"/>
-    <cellStyle name="Normal 3 6" xfId="3" xr:uid="{0DE30895-D5B6-4F42-8773-FC3E05E857CB}"/>
-    <cellStyle name="Normal 3 6 2" xfId="18" xr:uid="{8ECA74BB-2D76-474D-9277-CB573693B101}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="8"/>
+    <cellStyle name="Normal 2 3" xfId="19"/>
+    <cellStyle name="Normal 3" xfId="14"/>
+    <cellStyle name="Normal 3 4 2" xfId="11"/>
+    <cellStyle name="Normal 3 6" xfId="3"/>
+    <cellStyle name="Normal 3 6 2" xfId="18"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2825,38 +2830,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC77EC90-AFE8-8B47-8DF8-3157BA035D21}">
-  <dimension ref="A1:AL310"/>
-  <sheetFormatPr defaultColWidth="4.3125" defaultRowHeight="15.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AL311"/>
+  <sheetFormatPr defaultColWidth="4.33203125" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="8" style="14" customWidth="1"/>
-    <col min="2" max="2" width="23.8125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="12.1875" style="81" customWidth="1"/>
-    <col min="4" max="4" width="7.1875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="54.3125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" style="81" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="54.33203125" style="13" customWidth="1"/>
     <col min="6" max="6" width="61" style="13" customWidth="1"/>
-    <col min="7" max="7" width="62.1875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="62.21875" style="13" customWidth="1"/>
     <col min="8" max="8" width="21" style="36" customWidth="1"/>
-    <col min="9" max="9" width="20.5" style="36" customWidth="1"/>
-    <col min="10" max="10" width="22.5" style="36" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" style="36" customWidth="1"/>
+    <col min="10" max="10" width="22.44140625" style="36" customWidth="1"/>
     <col min="11" max="11" width="24" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.6875" style="67" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" style="67" customWidth="1"/>
     <col min="13" max="14" width="19" style="36" customWidth="1"/>
-    <col min="15" max="15" width="24.1875" style="36" customWidth="1"/>
+    <col min="15" max="15" width="24.21875" style="36" customWidth="1"/>
     <col min="16" max="16" width="25" style="36" customWidth="1"/>
-    <col min="17" max="18" width="19.3125" style="36" customWidth="1"/>
-    <col min="19" max="19" width="18.6875" style="36" customWidth="1"/>
-    <col min="20" max="20" width="14.5" style="36" customWidth="1"/>
-    <col min="21" max="21" width="18.5" style="36" customWidth="1"/>
-    <col min="22" max="22" width="18.8125" style="36" customWidth="1"/>
+    <col min="17" max="18" width="19.33203125" style="36" customWidth="1"/>
+    <col min="19" max="19" width="18.6640625" style="36" customWidth="1"/>
+    <col min="20" max="20" width="14.44140625" style="36" customWidth="1"/>
+    <col min="21" max="21" width="18.44140625" style="36" customWidth="1"/>
+    <col min="22" max="22" width="18.77734375" style="36" customWidth="1"/>
     <col min="23" max="23" width="20" style="36" customWidth="1"/>
-    <col min="24" max="24" width="21.6875" style="36" customWidth="1"/>
+    <col min="24" max="24" width="21.6640625" style="36" customWidth="1"/>
     <col min="25" max="25" width="6" style="43" customWidth="1"/>
-    <col min="26" max="26" width="20.8125" style="43" customWidth="1"/>
+    <col min="26" max="26" width="20.77734375" style="43" customWidth="1"/>
     <col min="27" max="27" width="19" style="36" customWidth="1"/>
-    <col min="28" max="29" width="21.1875" style="36" customWidth="1"/>
-    <col min="30" max="30" width="72.6875" style="13" customWidth="1"/>
-    <col min="31" max="16384" width="4.3125" style="13"/>
+    <col min="28" max="29" width="21.21875" style="36" customWidth="1"/>
+    <col min="30" max="30" width="72.6640625" style="13" customWidth="1"/>
+    <col min="31" max="16384" width="4.33203125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -2871,18 +2876,18 @@
         <v>0.02</v>
       </c>
       <c r="J1" s="36">
-        <f>K304-J304</f>
-        <v>38615675181</v>
+        <f>K305-J305</f>
+        <v>38815032737</v>
       </c>
       <c r="K1" s="36">
         <f>I1*J1</f>
-        <v>772313503.62</v>
+        <v>776300654.74000001</v>
       </c>
       <c r="L1" s="85" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="15.9" thickBot="1">
+    <row r="2" spans="1:38" ht="16.5" thickBot="1">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2915,7 +2920,7 @@
       </c>
       <c r="Z2" s="44"/>
     </row>
-    <row r="3" spans="1:38" ht="15.9" thickBot="1">
+    <row r="3" spans="1:38" ht="16.5" thickBot="1">
       <c r="A3" s="11" t="s">
         <v>47</v>
       </c>
@@ -2975,7 +2980,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:38" s="14" customFormat="1" ht="15.9" thickBot="1">
+    <row r="4" spans="1:38" s="14" customFormat="1" ht="16.5" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -26687,11 +26692,11 @@
         <v>0</v>
       </c>
       <c r="AA256" s="62">
-        <f t="shared" ref="AA256:AA302" si="38">-(H256+I256)*2%</f>
+        <f t="shared" ref="AA256:AA303" si="38">-(H256+I256)*2%</f>
         <v>0</v>
       </c>
       <c r="AB256" s="62">
-        <f t="shared" ref="AB256:AB302" si="39">K256+Z256+AA256</f>
+        <f t="shared" ref="AB256:AB303" si="39">K256+Z256+AA256</f>
         <v>0</v>
       </c>
       <c r="AC256" s="75">
@@ -27100,7 +27105,7 @@
         <v>0</v>
       </c>
       <c r="K261" s="72">
-        <f t="shared" ref="K261:K324" si="40">SUM(H261:J261)</f>
+        <f t="shared" ref="K261:K303" si="40">SUM(H261:J261)</f>
         <v>0</v>
       </c>
       <c r="L261" s="71"/>
@@ -27138,12 +27143,12 @@
         <v>0</v>
       </c>
       <c r="X261" s="62">
-        <f t="shared" ref="X261:X324" si="41">K261-SUM(M261:W261)</f>
+        <f t="shared" ref="X261:X303" si="41">K261-SUM(M261:W261)</f>
         <v>0</v>
       </c>
       <c r="Y261" s="62"/>
       <c r="Z261" s="73">
-        <f t="shared" ref="Z261:Z302" si="42">-J261</f>
+        <f t="shared" ref="Z261:Z303" si="42">-J261</f>
         <v>0</v>
       </c>
       <c r="AA261" s="62">
@@ -30797,299 +30802,388 @@
       </c>
       <c r="AD302" s="7"/>
     </row>
-    <row r="304" spans="1:30">
-      <c r="H304" s="95">
-        <f>SUBTOTAL(9,H5:H303)</f>
-        <v>36650779731</v>
-      </c>
-      <c r="I304" s="95">
-        <f>SUBTOTAL(9,I5:I303)</f>
-        <v>1964895450</v>
-      </c>
-      <c r="J304" s="95">
-        <f>SUBTOTAL(9,J5:J303)</f>
-        <v>3387129765</v>
-      </c>
-      <c r="K304" s="95">
-        <f>SUBTOTAL(9,K5:K303)</f>
-        <v>42002804946</v>
-      </c>
-      <c r="M304" s="32">
-        <f t="shared" ref="M304:X304" si="44">SUBTOTAL(9,M5:M303)</f>
+    <row r="303" spans="1:30" s="21" customFormat="1">
+      <c r="A303" s="19"/>
+      <c r="B303" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="C303" s="79">
+        <v>46097</v>
+      </c>
+      <c r="D303" s="25">
+        <v>2026</v>
+      </c>
+      <c r="E303" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F303" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G303" s="31" t="s">
+        <v>650</v>
+      </c>
+      <c r="H303" s="55">
+        <v>196018396</v>
+      </c>
+      <c r="I303" s="55">
+        <v>3339160</v>
+      </c>
+      <c r="J303" s="55">
+        <v>21929331</v>
+      </c>
+      <c r="K303" s="40">
+        <f t="shared" si="40"/>
+        <v>221286887</v>
+      </c>
+      <c r="L303" s="55"/>
+      <c r="M303" s="55">
+        <v>0</v>
+      </c>
+      <c r="N303" s="55">
+        <v>0</v>
+      </c>
+      <c r="O303" s="55">
+        <v>0</v>
+      </c>
+      <c r="P303" s="55">
+        <v>0</v>
+      </c>
+      <c r="Q303" s="55">
+        <v>0</v>
+      </c>
+      <c r="R303" s="55">
+        <v>0</v>
+      </c>
+      <c r="S303" s="55">
+        <v>0</v>
+      </c>
+      <c r="T303" s="55">
+        <v>0</v>
+      </c>
+      <c r="U303" s="55">
+        <v>0</v>
+      </c>
+      <c r="V303" s="55">
+        <v>0</v>
+      </c>
+      <c r="W303" s="55">
+        <v>0</v>
+      </c>
+      <c r="X303" s="39">
+        <f t="shared" si="41"/>
+        <v>221286887</v>
+      </c>
+      <c r="Y303" s="42"/>
+      <c r="Z303" s="8">
+        <f t="shared" si="42"/>
+        <v>-21929331</v>
+      </c>
+      <c r="AA303" s="42">
+        <f t="shared" si="38"/>
+        <v>-3987151.12</v>
+      </c>
+      <c r="AB303" s="42">
+        <f t="shared" si="39"/>
+        <v>195370404.88</v>
+      </c>
+      <c r="AC303" s="55">
+        <v>0</v>
+      </c>
+      <c r="AD303" s="7"/>
+    </row>
+    <row r="305" spans="1:29">
+      <c r="H305" s="95">
+        <f>SUBTOTAL(9,H5:H304)</f>
+        <v>36846798127</v>
+      </c>
+      <c r="I305" s="95">
+        <f>SUBTOTAL(9,I5:I304)</f>
+        <v>1968234610</v>
+      </c>
+      <c r="J305" s="95">
+        <f>SUBTOTAL(9,J5:J304)</f>
+        <v>3409059096</v>
+      </c>
+      <c r="K305" s="95">
+        <f>SUBTOTAL(9,K5:K304)</f>
+        <v>42224091833</v>
+      </c>
+      <c r="M305" s="32">
+        <f t="shared" ref="M305:X305" si="44">SUBTOTAL(9,M5:M304)</f>
         <v>3219609931</v>
       </c>
-      <c r="N304" s="32">
+      <c r="N305" s="32">
         <f t="shared" si="44"/>
         <v>4487221366</v>
       </c>
-      <c r="O304" s="32">
+      <c r="O305" s="32">
         <f t="shared" si="44"/>
         <v>16837158203.34</v>
       </c>
-      <c r="P304" s="32">
+      <c r="P305" s="32">
         <f t="shared" si="44"/>
         <v>3819509838.0999999</v>
       </c>
-      <c r="Q304" s="86">
+      <c r="Q305" s="86">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="R304" s="32">
+      <c r="R305" s="32">
         <f t="shared" si="44"/>
         <v>3915394741</v>
       </c>
-      <c r="S304" s="32">
+      <c r="S305" s="32">
         <f t="shared" si="44"/>
         <v>2978073566</v>
       </c>
-      <c r="T304" s="86">
+      <c r="T305" s="86">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="U304" s="32">
+      <c r="U305" s="32">
         <f t="shared" si="44"/>
         <v>1151031287</v>
       </c>
-      <c r="V304" s="86">
+      <c r="V305" s="86">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="W304" s="32">
+      <c r="W305" s="32">
         <f t="shared" si="44"/>
         <v>3154953380.5599999</v>
       </c>
-      <c r="X304" s="32">
+      <c r="X305" s="32">
         <f t="shared" si="44"/>
-        <v>2439852633</v>
-      </c>
-      <c r="Z304" s="32">
-        <f>SUBTOTAL(9,Z5:Z303)</f>
-        <v>-3387129765</v>
-      </c>
-      <c r="AA304" s="32">
-        <f>SUBTOTAL(9,AA5:AA303)</f>
-        <v>-557119534.24000001</v>
-      </c>
-      <c r="AB304" s="32">
-        <f>SUBTOTAL(9,AB5:AB303)</f>
-        <v>24846983243.66</v>
-      </c>
-      <c r="AC304" s="32">
-        <f>SUBTOTAL(9,AC5:AC303)</f>
+        <v>2661139520</v>
+      </c>
+      <c r="Z305" s="32">
+        <f>SUBTOTAL(9,Z5:Z304)</f>
+        <v>-3409059096</v>
+      </c>
+      <c r="AA305" s="32">
+        <f>SUBTOTAL(9,AA5:AA304)</f>
+        <v>-561106685.36000001</v>
+      </c>
+      <c r="AB305" s="32">
+        <f>SUBTOTAL(9,AB5:AB304)</f>
+        <v>25042353648.540001</v>
+      </c>
+      <c r="AC305" s="32">
+        <f>SUBTOTAL(9,AC5:AC304)</f>
         <v>10727544248.1</v>
       </c>
     </row>
-    <row r="305" spans="1:29">
-      <c r="H305" s="95"/>
-      <c r="I305" s="95"/>
-      <c r="J305" s="95"/>
-      <c r="K305" s="95"/>
-      <c r="M305" s="32"/>
-      <c r="N305" s="32"/>
-      <c r="O305" s="32"/>
-      <c r="P305" s="32"/>
-      <c r="Q305" s="32"/>
-      <c r="R305" s="32"/>
-      <c r="S305" s="32"/>
-      <c r="T305" s="32"/>
-      <c r="U305" s="32"/>
-      <c r="V305" s="32"/>
-      <c r="W305" s="32"/>
-      <c r="X305" s="32"/>
-      <c r="Z305" s="32"/>
-      <c r="AA305" s="32"/>
-      <c r="AB305" s="32"/>
-      <c r="AC305" s="32"/>
+    <row r="306" spans="1:29">
+      <c r="H306" s="95"/>
+      <c r="I306" s="95"/>
+      <c r="J306" s="95"/>
+      <c r="K306" s="95"/>
+      <c r="M306" s="32"/>
+      <c r="N306" s="32"/>
+      <c r="O306" s="32"/>
+      <c r="P306" s="32"/>
+      <c r="Q306" s="32"/>
+      <c r="R306" s="32"/>
+      <c r="S306" s="32"/>
+      <c r="T306" s="32"/>
+      <c r="U306" s="32"/>
+      <c r="V306" s="32"/>
+      <c r="W306" s="32"/>
+      <c r="X306" s="32"/>
+      <c r="Z306" s="32"/>
+      <c r="AA306" s="32"/>
+      <c r="AB306" s="32"/>
+      <c r="AC306" s="32"/>
     </row>
-    <row r="306" spans="1:29" s="35" customFormat="1">
-      <c r="A306" s="64"/>
-      <c r="C306" s="70"/>
-      <c r="D306" s="64"/>
-      <c r="H306" s="72"/>
-      <c r="I306" s="72"/>
-      <c r="J306" s="72"/>
-      <c r="K306" s="72"/>
-      <c r="L306" s="70"/>
-      <c r="M306" s="65">
+    <row r="307" spans="1:29" s="35" customFormat="1">
+      <c r="A307" s="64"/>
+      <c r="C307" s="70"/>
+      <c r="D307" s="64"/>
+      <c r="H307" s="72"/>
+      <c r="I307" s="72"/>
+      <c r="J307" s="72"/>
+      <c r="K307" s="72"/>
+      <c r="L307" s="70"/>
+      <c r="M307" s="65">
         <v>3219609931</v>
       </c>
-      <c r="N306" s="65">
+      <c r="N307" s="65">
         <v>4487221366</v>
       </c>
-      <c r="O306" s="65">
+      <c r="O307" s="65">
         <v>16837158203.34</v>
       </c>
-      <c r="P306" s="65">
+      <c r="P307" s="65">
         <v>3819509838.0999999</v>
       </c>
-      <c r="Q306" s="65"/>
-      <c r="R306" s="65">
+      <c r="Q307" s="65"/>
+      <c r="R307" s="65">
         <v>3915394741</v>
       </c>
-      <c r="S306" s="65">
+      <c r="S307" s="65">
         <v>2978073566</v>
       </c>
-      <c r="T306" s="65"/>
-      <c r="U306" s="65">
+      <c r="T307" s="65"/>
+      <c r="U307" s="65">
         <v>1151031287</v>
       </c>
-      <c r="V306" s="65"/>
-      <c r="W306" s="65">
+      <c r="V307" s="65"/>
+      <c r="W307" s="65">
         <v>3154953380.5599999</v>
       </c>
-      <c r="X306" s="65"/>
-      <c r="Y306" s="66"/>
-      <c r="Z306" s="65"/>
-      <c r="AA306" s="65"/>
-      <c r="AB306" s="65"/>
-      <c r="AC306" s="65"/>
+      <c r="X307" s="65"/>
+      <c r="Y307" s="66"/>
+      <c r="Z307" s="65"/>
+      <c r="AA307" s="65"/>
+      <c r="AB307" s="65"/>
+      <c r="AC307" s="65"/>
     </row>
-    <row r="307" spans="1:29">
-      <c r="H307" s="95"/>
-      <c r="I307" s="95"/>
-      <c r="J307" s="95"/>
-      <c r="K307" s="95"/>
-      <c r="M307" s="32"/>
-      <c r="N307" s="32"/>
-      <c r="O307" s="32"/>
-      <c r="P307" s="32"/>
-      <c r="Q307" s="32"/>
-      <c r="R307" s="32"/>
-      <c r="S307" s="32"/>
-      <c r="T307" s="32"/>
-      <c r="U307" s="32"/>
-      <c r="V307" s="32"/>
-      <c r="W307" s="32"/>
-      <c r="X307" s="32"/>
-      <c r="Z307" s="32"/>
-      <c r="AA307" s="32"/>
-      <c r="AB307" s="32"/>
-      <c r="AC307" s="32"/>
+    <row r="308" spans="1:29">
+      <c r="H308" s="95"/>
+      <c r="I308" s="95"/>
+      <c r="J308" s="95"/>
+      <c r="K308" s="95"/>
+      <c r="M308" s="32"/>
+      <c r="N308" s="32"/>
+      <c r="O308" s="32"/>
+      <c r="P308" s="32"/>
+      <c r="Q308" s="32"/>
+      <c r="R308" s="32"/>
+      <c r="S308" s="32"/>
+      <c r="T308" s="32"/>
+      <c r="U308" s="32"/>
+      <c r="V308" s="32"/>
+      <c r="W308" s="32"/>
+      <c r="X308" s="32"/>
+      <c r="Z308" s="32"/>
+      <c r="AA308" s="32"/>
+      <c r="AB308" s="32"/>
+      <c r="AC308" s="32"/>
     </row>
-    <row r="308" spans="1:29" s="22" customFormat="1">
-      <c r="A308" s="28"/>
-      <c r="C308" s="69"/>
-      <c r="D308" s="28"/>
-      <c r="H308" s="41"/>
-      <c r="I308" s="41"/>
-      <c r="J308" s="41"/>
-      <c r="K308" s="41"/>
-      <c r="L308" s="69"/>
-      <c r="M308" s="29">
-        <f>M304-M306</f>
-        <v>0</v>
-      </c>
-      <c r="N308" s="29">
-        <f>N304-N306</f>
-        <v>0</v>
-      </c>
-      <c r="O308" s="29">
-        <f>O304-O306</f>
-        <v>0</v>
-      </c>
-      <c r="P308" s="29">
-        <f>P304-P306</f>
-        <v>0</v>
-      </c>
-      <c r="Q308" s="29"/>
-      <c r="R308" s="29">
-        <f>R304-R306</f>
-        <v>0</v>
-      </c>
-      <c r="S308" s="29">
-        <f>S304-S306</f>
-        <v>0</v>
-      </c>
-      <c r="T308" s="29">
-        <f>T304-T306</f>
-        <v>0</v>
-      </c>
-      <c r="U308" s="29">
-        <f>U304-U306</f>
-        <v>0</v>
-      </c>
-      <c r="V308" s="29"/>
-      <c r="W308" s="29">
-        <f>W304-W306</f>
-        <v>0</v>
-      </c>
-      <c r="X308" s="29"/>
-      <c r="Y308" s="56"/>
-      <c r="Z308" s="29"/>
-      <c r="AA308" s="29"/>
-      <c r="AB308" s="29"/>
-      <c r="AC308" s="29"/>
+    <row r="309" spans="1:29" s="22" customFormat="1">
+      <c r="A309" s="28"/>
+      <c r="C309" s="69"/>
+      <c r="D309" s="28"/>
+      <c r="H309" s="41"/>
+      <c r="I309" s="41"/>
+      <c r="J309" s="41"/>
+      <c r="K309" s="41"/>
+      <c r="L309" s="69"/>
+      <c r="M309" s="29">
+        <f>M305-M307</f>
+        <v>0</v>
+      </c>
+      <c r="N309" s="29">
+        <f>N305-N307</f>
+        <v>0</v>
+      </c>
+      <c r="O309" s="29">
+        <f>O305-O307</f>
+        <v>0</v>
+      </c>
+      <c r="P309" s="29">
+        <f>P305-P307</f>
+        <v>0</v>
+      </c>
+      <c r="Q309" s="29"/>
+      <c r="R309" s="29">
+        <f>R305-R307</f>
+        <v>0</v>
+      </c>
+      <c r="S309" s="29">
+        <f>S305-S307</f>
+        <v>0</v>
+      </c>
+      <c r="T309" s="29">
+        <f>T305-T307</f>
+        <v>0</v>
+      </c>
+      <c r="U309" s="29">
+        <f>U305-U307</f>
+        <v>0</v>
+      </c>
+      <c r="V309" s="29"/>
+      <c r="W309" s="29">
+        <f>W305-W307</f>
+        <v>0</v>
+      </c>
+      <c r="X309" s="29"/>
+      <c r="Y309" s="56"/>
+      <c r="Z309" s="29"/>
+      <c r="AA309" s="29"/>
+      <c r="AB309" s="29"/>
+      <c r="AC309" s="29"/>
     </row>
-    <row r="309" spans="1:29">
-      <c r="H309" s="95"/>
-      <c r="I309" s="95"/>
-      <c r="J309" s="95"/>
-      <c r="K309" s="95"/>
-      <c r="M309" s="32"/>
-      <c r="N309" s="32"/>
-      <c r="O309" s="32"/>
-      <c r="P309" s="32"/>
-      <c r="Q309" s="32"/>
-      <c r="R309" s="32"/>
-      <c r="S309" s="32"/>
-      <c r="T309" s="32"/>
-      <c r="U309" s="32"/>
-      <c r="V309" s="32"/>
-      <c r="W309" s="32"/>
-      <c r="X309" s="32"/>
-      <c r="Z309" s="32"/>
-      <c r="AA309" s="32"/>
-      <c r="AB309" s="32"/>
-      <c r="AC309" s="32"/>
+    <row r="310" spans="1:29">
+      <c r="H310" s="95"/>
+      <c r="I310" s="95"/>
+      <c r="J310" s="95"/>
+      <c r="K310" s="95"/>
+      <c r="M310" s="32"/>
+      <c r="N310" s="32"/>
+      <c r="O310" s="32"/>
+      <c r="P310" s="32"/>
+      <c r="Q310" s="32"/>
+      <c r="R310" s="32"/>
+      <c r="S310" s="32"/>
+      <c r="T310" s="32"/>
+      <c r="U310" s="32"/>
+      <c r="V310" s="32"/>
+      <c r="W310" s="32"/>
+      <c r="X310" s="32"/>
+      <c r="Z310" s="32"/>
+      <c r="AA310" s="32"/>
+      <c r="AB310" s="32"/>
+      <c r="AC310" s="32"/>
     </row>
-    <row r="310" spans="1:29" s="22" customFormat="1">
-      <c r="A310" s="28"/>
-      <c r="B310" s="7" t="s">
+    <row r="311" spans="1:29" s="22" customFormat="1">
+      <c r="A311" s="28"/>
+      <c r="B311" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C310" s="80" t="s">
+      <c r="C311" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D310" s="25" t="s">
+      <c r="D311" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="E310" s="22" t="s">
+      <c r="E311" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F310" s="22" t="s">
+      <c r="F311" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="G310" s="22" t="s">
+      <c r="G311" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H310" s="41" t="s">
+      <c r="H311" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="I310" s="41"/>
-      <c r="J310" s="41"/>
-      <c r="K310" s="41"/>
-      <c r="L310" s="69"/>
-      <c r="M310" s="41"/>
-      <c r="N310" s="41"/>
-      <c r="O310" s="41"/>
-      <c r="P310" s="41"/>
-      <c r="Q310" s="41"/>
-      <c r="R310" s="41"/>
-      <c r="S310" s="41"/>
-      <c r="T310" s="41"/>
-      <c r="U310" s="41"/>
-      <c r="V310" s="41"/>
-      <c r="W310" s="41"/>
-      <c r="X310" s="41"/>
-      <c r="Y310" s="63"/>
-      <c r="Z310" s="63"/>
-      <c r="AA310" s="41"/>
-      <c r="AB310" s="41"/>
-      <c r="AC310" s="41"/>
+      <c r="I311" s="41"/>
+      <c r="J311" s="41"/>
+      <c r="K311" s="41"/>
+      <c r="L311" s="69"/>
+      <c r="M311" s="41"/>
+      <c r="N311" s="41"/>
+      <c r="O311" s="41"/>
+      <c r="P311" s="41"/>
+      <c r="Q311" s="41"/>
+      <c r="R311" s="41"/>
+      <c r="S311" s="41"/>
+      <c r="T311" s="41"/>
+      <c r="U311" s="41"/>
+      <c r="V311" s="41"/>
+      <c r="W311" s="41"/>
+      <c r="X311" s="41"/>
+      <c r="Y311" s="63"/>
+      <c r="Z311" s="63"/>
+      <c r="AA311" s="41"/>
+      <c r="AB311" s="41"/>
+      <c r="AC311" s="41"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AD302" xr:uid="{1C42E8D8-1C34-4746-A665-F5E7C855E98B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AD302">
+  <autoFilter ref="A4:AD302">
+    <sortState ref="A5:AD302">
       <sortCondition sortBy="fontColor" ref="J4:J302" dxfId="0"/>
     </sortState>
   </autoFilter>

--- a/backend/prisma/seed-data/sales.xlsx
+++ b/backend/prisma/seed-data/sales.xlsx
@@ -9,15 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="24885" windowHeight="14910"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17685"/>
   </bookViews>
   <sheets>
-    <sheet name="Inv 10-Feb-26" sheetId="43" r:id="rId1"/>
+    <sheet name="List Invoice" sheetId="43" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inv 10-Feb-26'!$A$4:$AD$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'List Invoice'!$A$4:$AD$302</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="654">
   <si>
     <t>Account Receivable</t>
   </si>
@@ -790,9 +790,6 @@
     <t>List of Invoices 2025</t>
   </si>
   <si>
-    <t>Date Received</t>
-  </si>
-  <si>
     <t>031/PCMI/AR/VI/2025</t>
   </si>
   <si>
@@ -1987,10 +1984,22 @@
     <t>Money Bucket Farewell Bu Henny</t>
   </si>
   <si>
+    <t>216/PCMI/AR/X/2025</t>
+  </si>
+  <si>
+    <t>Pengadaan untuk ANO Sumatera Forum 2025</t>
+  </si>
+  <si>
     <t>044/97/PCMI/AR/II/2026</t>
   </si>
   <si>
-    <t>Pengadaan untuk ANO Sumatera Forum 2025</t>
+    <t>072/271/PCMI/AR/V/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Souvenirs Eksklusif Korporat </t>
+  </si>
+  <si>
+    <t>Faktur PPN WAPU masuk dalam laporan tahun 2026</t>
   </si>
 </sst>
 </file>
@@ -2001,10 +2010,10 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2080,6 +2089,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2246,8 +2262,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2255,13 +2271,13 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2280,11 +2296,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2317,7 +2333,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2331,14 +2347,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="15" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2346,77 +2362,77 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="14" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2432,12 +2448,12 @@
     <xf numFmtId="15" fontId="6" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2460,38 +2476,41 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -2831,23 +2850,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL311"/>
+  <dimension ref="A1:AL310"/>
   <sheetFormatPr defaultColWidth="4.33203125" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="8" style="14" customWidth="1"/>
     <col min="2" max="2" width="23.77734375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="81" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="81" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" style="14" customWidth="1"/>
     <col min="5" max="5" width="54.33203125" style="13" customWidth="1"/>
     <col min="6" max="6" width="61" style="13" customWidth="1"/>
-    <col min="7" max="7" width="62.21875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="62.109375" style="13" customWidth="1"/>
     <col min="8" max="8" width="21" style="36" customWidth="1"/>
     <col min="9" max="9" width="20.44140625" style="36" customWidth="1"/>
     <col min="10" max="10" width="22.44140625" style="36" customWidth="1"/>
     <col min="11" max="11" width="24" style="36" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" style="67" customWidth="1"/>
+    <col min="12" max="12" width="5.44140625" style="67" customWidth="1"/>
     <col min="13" max="14" width="19" style="36" customWidth="1"/>
-    <col min="15" max="15" width="24.21875" style="36" customWidth="1"/>
+    <col min="15" max="15" width="24.109375" style="36" customWidth="1"/>
     <col min="16" max="16" width="25" style="36" customWidth="1"/>
     <col min="17" max="18" width="19.33203125" style="36" customWidth="1"/>
     <col min="19" max="19" width="18.6640625" style="36" customWidth="1"/>
@@ -2859,7 +2878,7 @@
     <col min="25" max="25" width="6" style="43" customWidth="1"/>
     <col min="26" max="26" width="20.77734375" style="43" customWidth="1"/>
     <col min="27" max="27" width="19" style="36" customWidth="1"/>
-    <col min="28" max="29" width="21.21875" style="36" customWidth="1"/>
+    <col min="28" max="29" width="21.109375" style="36" customWidth="1"/>
     <col min="30" max="30" width="72.6640625" style="13" customWidth="1"/>
     <col min="31" max="16384" width="4.33203125" style="13"/>
   </cols>
@@ -2872,20 +2891,16 @@
       <c r="C1" s="2"/>
       <c r="D1" s="19"/>
       <c r="F1" s="22"/>
-      <c r="I1" s="36">
-        <v>0.02</v>
-      </c>
-      <c r="J1" s="36">
-        <f>K305-J305</f>
-        <v>38815032737</v>
-      </c>
-      <c r="K1" s="36">
-        <f>I1*J1</f>
-        <v>776300654.74000001</v>
-      </c>
-      <c r="L1" s="85" t="s">
+      <c r="I1" s="36" t="s">
         <v>1</v>
       </c>
+      <c r="J1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="85"/>
     </row>
     <row r="2" spans="1:38" ht="16.5" thickBot="1">
       <c r="B2" s="3" t="s">
@@ -2912,9 +2927,7 @@
       <c r="J2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="34" t="s">
-        <v>1</v>
-      </c>
+      <c r="L2" s="34"/>
       <c r="P2" s="62" t="s">
         <v>1</v>
       </c>
@@ -3002,9 +3015,7 @@
       <c r="K4" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="34" t="s">
-        <v>250</v>
-      </c>
+      <c r="L4" s="34"/>
       <c r="M4" s="52" t="s">
         <v>63</v>
       </c>
@@ -3012,10 +3023,10 @@
         <v>62</v>
       </c>
       <c r="O4" s="38" t="s">
+        <v>522</v>
+      </c>
+      <c r="P4" s="38" t="s">
         <v>523</v>
-      </c>
-      <c r="P4" s="38" t="s">
-        <v>524</v>
       </c>
       <c r="Q4" s="38" t="s">
         <v>60</v>
@@ -3088,9 +3099,7 @@
         <f t="shared" ref="K5:K68" si="0">SUM(H5:J5)</f>
         <v>83250000</v>
       </c>
-      <c r="L5" s="34">
-        <v>45721</v>
-      </c>
+      <c r="L5" s="34"/>
       <c r="M5" s="40">
         <v>0</v>
       </c>
@@ -3182,9 +3191,7 @@
         <f t="shared" si="0"/>
         <v>750000000</v>
       </c>
-      <c r="L6" s="34">
-        <v>45720</v>
-      </c>
+      <c r="L6" s="34"/>
       <c r="M6" s="40">
         <v>0</v>
       </c>
@@ -3286,9 +3293,7 @@
         <f t="shared" si="0"/>
         <v>250000000</v>
       </c>
-      <c r="L7" s="34">
-        <v>45705</v>
-      </c>
+      <c r="L7" s="34"/>
       <c r="M7" s="40">
         <v>0</v>
       </c>
@@ -3380,9 +3385,7 @@
         <f t="shared" si="0"/>
         <v>83250000</v>
       </c>
-      <c r="L8" s="34">
-        <v>45756</v>
-      </c>
+      <c r="L8" s="34"/>
       <c r="M8" s="40">
         <v>0</v>
       </c>
@@ -3474,9 +3477,7 @@
         <f t="shared" si="0"/>
         <v>750000000</v>
       </c>
-      <c r="L9" s="34">
-        <v>45706</v>
-      </c>
+      <c r="L9" s="34"/>
       <c r="M9" s="40">
         <v>0</v>
       </c>
@@ -3568,9 +3569,7 @@
         <f t="shared" si="0"/>
         <v>12276600</v>
       </c>
-      <c r="L10" s="34">
-        <v>45701</v>
-      </c>
+      <c r="L10" s="34"/>
       <c r="M10" s="40">
         <v>0</v>
       </c>
@@ -3662,9 +3661,7 @@
         <f t="shared" si="0"/>
         <v>500000000</v>
       </c>
-      <c r="L11" s="34">
-        <v>45902</v>
-      </c>
+      <c r="L11" s="34"/>
       <c r="M11" s="40">
         <v>0</v>
       </c>
@@ -3756,9 +3753,7 @@
         <f t="shared" si="0"/>
         <v>100000000</v>
       </c>
-      <c r="L12" s="34">
-        <v>45706</v>
-      </c>
+      <c r="L12" s="34"/>
       <c r="M12" s="40">
         <v>0</v>
       </c>
@@ -3856,9 +3851,7 @@
         <f t="shared" si="0"/>
         <v>55500000</v>
       </c>
-      <c r="L13" s="34">
-        <v>45707</v>
-      </c>
+      <c r="L13" s="34"/>
       <c r="M13" s="40">
         <v>0</v>
       </c>
@@ -3932,10 +3925,10 @@
         <v>42</v>
       </c>
       <c r="F14" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="G14" s="20" t="s">
         <v>610</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>611</v>
       </c>
       <c r="H14" s="55">
         <v>10825000</v>
@@ -3950,9 +3943,7 @@
         <f t="shared" si="0"/>
         <v>12015750</v>
       </c>
-      <c r="L14" s="34">
-        <v>45737</v>
-      </c>
+      <c r="L14" s="34"/>
       <c r="M14" s="40">
         <v>0</v>
       </c>
@@ -4044,9 +4035,7 @@
         <f t="shared" si="0"/>
         <v>100000000</v>
       </c>
-      <c r="L15" s="34">
-        <v>45719</v>
-      </c>
+      <c r="L15" s="34"/>
       <c r="M15" s="40">
         <v>0</v>
       </c>
@@ -4123,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H16" s="55">
         <v>0</v>
@@ -4230,9 +4219,7 @@
         <f t="shared" si="0"/>
         <v>250000000</v>
       </c>
-      <c r="L17" s="34">
-        <v>45720</v>
-      </c>
+      <c r="L17" s="34"/>
       <c r="M17" s="40">
         <v>0</v>
       </c>
@@ -4324,9 +4311,7 @@
         <f t="shared" si="0"/>
         <v>250000000</v>
       </c>
-      <c r="L18" s="34">
-        <v>45721</v>
-      </c>
+      <c r="L18" s="34"/>
       <c r="M18" s="40">
         <v>0</v>
       </c>
@@ -4418,9 +4403,7 @@
         <f t="shared" si="0"/>
         <v>75000000</v>
       </c>
-      <c r="L19" s="34">
-        <v>45777</v>
-      </c>
+      <c r="L19" s="34"/>
       <c r="M19" s="40">
         <v>0</v>
       </c>
@@ -4515,9 +4498,7 @@
         <f t="shared" si="0"/>
         <v>693750000</v>
       </c>
-      <c r="L20" s="34">
-        <v>45791</v>
-      </c>
+      <c r="L20" s="34"/>
       <c r="M20" s="40">
         <v>0</v>
       </c>
@@ -4609,9 +4590,7 @@
         <f t="shared" si="0"/>
         <v>250000000</v>
       </c>
-      <c r="L21" s="34">
-        <v>45705</v>
-      </c>
+      <c r="L21" s="34"/>
       <c r="M21" s="40">
         <v>0</v>
       </c>
@@ -4703,9 +4682,7 @@
         <f t="shared" si="0"/>
         <v>100000000</v>
       </c>
-      <c r="L22" s="34">
-        <v>45720</v>
-      </c>
+      <c r="L22" s="34"/>
       <c r="M22" s="40">
         <v>0</v>
       </c>
@@ -4797,9 +4774,7 @@
         <f t="shared" si="0"/>
         <v>100000000</v>
       </c>
-      <c r="L23" s="34">
-        <v>45911</v>
-      </c>
+      <c r="L23" s="34"/>
       <c r="M23" s="40">
         <v>0</v>
       </c>
@@ -4891,9 +4866,7 @@
         <f t="shared" si="0"/>
         <v>33300000</v>
       </c>
-      <c r="L24" s="34">
-        <v>45786</v>
-      </c>
+      <c r="L24" s="34"/>
       <c r="M24" s="40">
         <v>0</v>
       </c>
@@ -4985,9 +4958,7 @@
         <f t="shared" si="0"/>
         <v>250000000</v>
       </c>
-      <c r="L25" s="34">
-        <v>45719</v>
-      </c>
+      <c r="L25" s="34"/>
       <c r="M25" s="40">
         <v>0</v>
       </c>
@@ -5079,9 +5050,7 @@
         <f t="shared" si="0"/>
         <v>50000000</v>
       </c>
-      <c r="L26" s="34">
-        <v>45940</v>
-      </c>
+      <c r="L26" s="34"/>
       <c r="M26" s="40">
         <v>0</v>
       </c>
@@ -5173,9 +5142,7 @@
         <f t="shared" si="0"/>
         <v>50000000</v>
       </c>
-      <c r="L27" s="34">
-        <v>45716</v>
-      </c>
+      <c r="L27" s="34"/>
       <c r="M27" s="40">
         <v>0</v>
       </c>
@@ -5268,9 +5235,7 @@
         <f t="shared" si="0"/>
         <v>55500000</v>
       </c>
-      <c r="L28" s="34">
-        <v>45707</v>
-      </c>
+      <c r="L28" s="34"/>
       <c r="M28" s="40">
         <v>0</v>
       </c>
@@ -5362,9 +5327,7 @@
         <f t="shared" si="0"/>
         <v>50000000</v>
       </c>
-      <c r="L29" s="34">
-        <v>45702</v>
-      </c>
+      <c r="L29" s="34"/>
       <c r="M29" s="40">
         <v>0</v>
       </c>
@@ -5456,9 +5419,7 @@
         <f t="shared" si="0"/>
         <v>50000000</v>
       </c>
-      <c r="L30" s="34">
-        <v>45715</v>
-      </c>
+      <c r="L30" s="34"/>
       <c r="M30" s="40">
         <v>0</v>
       </c>
@@ -5550,9 +5511,7 @@
         <f t="shared" si="0"/>
         <v>50000000</v>
       </c>
-      <c r="L31" s="34">
-        <v>45722</v>
-      </c>
+      <c r="L31" s="34"/>
       <c r="M31" s="40">
         <v>0</v>
       </c>
@@ -5614,7 +5573,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C32" s="4">
         <v>45811</v>
@@ -5644,9 +5603,7 @@
         <f t="shared" si="0"/>
         <v>35000000</v>
       </c>
-      <c r="L32" s="34">
-        <v>45824</v>
-      </c>
+      <c r="L32" s="34"/>
       <c r="M32" s="40">
         <v>0</v>
       </c>
@@ -5738,9 +5695,7 @@
         <f t="shared" si="0"/>
         <v>100000000</v>
       </c>
-      <c r="L33" s="34">
-        <v>45709</v>
-      </c>
+      <c r="L33" s="34"/>
       <c r="M33" s="40">
         <v>0</v>
       </c>
@@ -5832,9 +5787,7 @@
         <f t="shared" si="0"/>
         <v>25000001</v>
       </c>
-      <c r="L34" s="34">
-        <v>45785</v>
-      </c>
+      <c r="L34" s="34"/>
       <c r="M34" s="40">
         <v>0</v>
       </c>
@@ -5926,9 +5879,7 @@
         <f t="shared" si="0"/>
         <v>250000000</v>
       </c>
-      <c r="L35" s="34">
-        <v>45734</v>
-      </c>
+      <c r="L35" s="34"/>
       <c r="M35" s="40">
         <v>0</v>
       </c>
@@ -6020,9 +5971,7 @@
         <f t="shared" si="0"/>
         <v>16650000</v>
       </c>
-      <c r="L36" s="34">
-        <v>45715</v>
-      </c>
+      <c r="L36" s="34"/>
       <c r="M36" s="40">
         <v>0</v>
       </c>
@@ -6114,9 +6063,7 @@
         <f t="shared" si="0"/>
         <v>55500000</v>
       </c>
-      <c r="L37" s="34">
-        <v>45727</v>
-      </c>
+      <c r="L37" s="34"/>
       <c r="M37" s="40">
         <v>0</v>
       </c>
@@ -6208,9 +6155,7 @@
         <f t="shared" si="0"/>
         <v>277500000</v>
       </c>
-      <c r="L38" s="34">
-        <v>45733</v>
-      </c>
+      <c r="L38" s="34"/>
       <c r="M38" s="40">
         <v>0</v>
       </c>
@@ -6302,9 +6247,7 @@
         <f t="shared" si="0"/>
         <v>83250000</v>
       </c>
-      <c r="L39" s="34">
-        <v>45713</v>
-      </c>
+      <c r="L39" s="34"/>
       <c r="M39" s="40">
         <v>0</v>
       </c>
@@ -6396,9 +6339,7 @@
         <f t="shared" si="0"/>
         <v>75000000</v>
       </c>
-      <c r="L40" s="34">
-        <v>45723</v>
-      </c>
+      <c r="L40" s="34"/>
       <c r="M40" s="40">
         <v>0</v>
       </c>
@@ -6490,9 +6431,7 @@
         <f t="shared" si="0"/>
         <v>75000000</v>
       </c>
-      <c r="L41" s="34">
-        <v>45723</v>
-      </c>
+      <c r="L41" s="34"/>
       <c r="M41" s="40">
         <v>0</v>
       </c>
@@ -6584,9 +6523,7 @@
         <f t="shared" si="0"/>
         <v>60000000</v>
       </c>
-      <c r="L42" s="34">
-        <v>45710</v>
-      </c>
+      <c r="L42" s="34"/>
       <c r="M42" s="40">
         <v>60000000</v>
       </c>
@@ -6659,10 +6596,10 @@
         <v>42</v>
       </c>
       <c r="F43" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="G43" s="20" t="s">
         <v>610</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>611</v>
       </c>
       <c r="H43" s="55">
         <v>10825000</v>
@@ -6677,9 +6614,7 @@
         <f t="shared" si="0"/>
         <v>12015750</v>
       </c>
-      <c r="L43" s="34">
-        <v>45737</v>
-      </c>
+      <c r="L43" s="34"/>
       <c r="M43" s="40">
         <v>0</v>
       </c>
@@ -6753,15 +6688,17 @@
         <v>42</v>
       </c>
       <c r="F44" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="G44" s="20" t="s">
         <v>610</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>611</v>
       </c>
       <c r="H44" s="55">
         <v>10750000</v>
       </c>
-      <c r="I44" s="55"/>
+      <c r="I44" s="55">
+        <v>0</v>
+      </c>
       <c r="J44" s="55">
         <v>1182500</v>
       </c>
@@ -6769,9 +6706,7 @@
         <f t="shared" si="0"/>
         <v>11932500</v>
       </c>
-      <c r="L44" s="34">
-        <v>45764</v>
-      </c>
+      <c r="L44" s="34"/>
       <c r="M44" s="40">
         <v>0</v>
       </c>
@@ -6863,9 +6798,7 @@
         <f t="shared" si="0"/>
         <v>2030000</v>
       </c>
-      <c r="L45" s="34">
-        <v>45705</v>
-      </c>
+      <c r="L45" s="34"/>
       <c r="M45" s="40">
         <v>2030000</v>
       </c>
@@ -6955,9 +6888,7 @@
         <f t="shared" si="0"/>
         <v>3043010</v>
       </c>
-      <c r="L46" s="34">
-        <v>45795</v>
-      </c>
+      <c r="L46" s="34"/>
       <c r="M46" s="40">
         <v>3043010</v>
       </c>
@@ -7047,9 +6978,7 @@
         <f t="shared" si="0"/>
         <v>188949750</v>
       </c>
-      <c r="L47" s="34">
-        <v>45728</v>
-      </c>
+      <c r="L47" s="34"/>
       <c r="M47" s="40">
         <v>0</v>
       </c>
@@ -7141,9 +7070,7 @@
         <f t="shared" si="0"/>
         <v>68100000</v>
       </c>
-      <c r="L48" s="34">
-        <v>45768</v>
-      </c>
+      <c r="L48" s="34"/>
       <c r="M48" s="40">
         <v>68100000</v>
       </c>
@@ -7234,9 +7161,7 @@
         <f t="shared" si="0"/>
         <v>89790120</v>
       </c>
-      <c r="L49" s="34">
-        <v>45734</v>
-      </c>
+      <c r="L49" s="34"/>
       <c r="M49" s="40">
         <v>0</v>
       </c>
@@ -7328,9 +7253,7 @@
         <f t="shared" si="0"/>
         <v>222107670</v>
       </c>
-      <c r="L50" s="34">
-        <v>45734</v>
-      </c>
+      <c r="L50" s="34"/>
       <c r="M50" s="40">
         <v>0</v>
       </c>
@@ -7422,9 +7345,7 @@
         <f t="shared" si="0"/>
         <v>1550000</v>
       </c>
-      <c r="L51" s="34">
-        <v>45838</v>
-      </c>
+      <c r="L51" s="34"/>
       <c r="M51" s="40">
         <v>1550000</v>
       </c>
@@ -7514,9 +7435,7 @@
         <f t="shared" si="0"/>
         <v>12807421</v>
       </c>
-      <c r="L52" s="34">
-        <v>45758</v>
-      </c>
+      <c r="L52" s="34"/>
       <c r="M52" s="40">
         <v>0</v>
       </c>
@@ -7608,9 +7527,7 @@
         <f t="shared" si="0"/>
         <v>52479191</v>
       </c>
-      <c r="L53" s="34">
-        <v>45771</v>
-      </c>
+      <c r="L53" s="34"/>
       <c r="M53" s="40">
         <v>0</v>
       </c>
@@ -7702,9 +7619,7 @@
         <f t="shared" si="0"/>
         <v>91025550</v>
       </c>
-      <c r="L54" s="34">
-        <v>45776</v>
-      </c>
+      <c r="L54" s="34"/>
       <c r="M54" s="40">
         <v>0</v>
       </c>
@@ -7796,9 +7711,7 @@
         <f t="shared" si="0"/>
         <v>227789760</v>
       </c>
-      <c r="L55" s="34">
-        <v>45791</v>
-      </c>
+      <c r="L55" s="34"/>
       <c r="M55" s="40">
         <v>0</v>
       </c>
@@ -7890,9 +7803,7 @@
         <f t="shared" si="0"/>
         <v>294413625</v>
       </c>
-      <c r="L56" s="34">
-        <v>45804</v>
-      </c>
+      <c r="L56" s="34"/>
       <c r="M56" s="40">
         <v>0</v>
       </c>
@@ -7984,9 +7895,7 @@
         <f t="shared" si="0"/>
         <v>575000000</v>
       </c>
-      <c r="L57" s="34">
-        <v>45805</v>
-      </c>
+      <c r="L57" s="34"/>
       <c r="M57" s="40">
         <v>0</v>
       </c>
@@ -8078,9 +7987,7 @@
         <f t="shared" si="0"/>
         <v>35000000</v>
       </c>
-      <c r="L58" s="34">
-        <v>45810</v>
-      </c>
+      <c r="L58" s="34"/>
       <c r="M58" s="40">
         <v>0</v>
       </c>
@@ -8172,9 +8079,7 @@
         <f t="shared" si="0"/>
         <v>18618641</v>
       </c>
-      <c r="L59" s="34">
-        <v>45821</v>
-      </c>
+      <c r="L59" s="34"/>
       <c r="M59" s="40">
         <v>0</v>
       </c>
@@ -8229,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="1:30" s="76" customFormat="1">
@@ -8268,9 +8173,7 @@
         <f t="shared" si="0"/>
         <v>21424884</v>
       </c>
-      <c r="L60" s="34">
-        <v>45821</v>
-      </c>
+      <c r="L60" s="34"/>
       <c r="M60" s="40">
         <v>0</v>
       </c>
@@ -8325,7 +8228,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="61" spans="1:30" s="21" customFormat="1">
@@ -8364,9 +8267,7 @@
         <f t="shared" si="0"/>
         <v>20728469</v>
       </c>
-      <c r="L61" s="34">
-        <v>45821</v>
-      </c>
+      <c r="L61" s="34"/>
       <c r="M61" s="40">
         <v>0</v>
       </c>
@@ -8421,7 +8322,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="62" spans="1:30" s="21" customFormat="1">
@@ -8430,7 +8331,7 @@
         <v>58</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C62" s="4">
         <v>45799</v>
@@ -8442,10 +8343,10 @@
         <v>42</v>
       </c>
       <c r="F62" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="G62" s="20" t="s">
         <v>263</v>
-      </c>
-      <c r="G62" s="20" t="s">
-        <v>264</v>
       </c>
       <c r="H62" s="55">
         <v>55000474</v>
@@ -8460,9 +8361,7 @@
         <f t="shared" si="0"/>
         <v>61050526</v>
       </c>
-      <c r="L62" s="34">
-        <v>45831</v>
-      </c>
+      <c r="L62" s="34"/>
       <c r="M62" s="40">
         <v>0</v>
       </c>
@@ -8524,7 +8423,7 @@
         <v>59</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C63" s="4">
         <v>45810</v>
@@ -8533,13 +8432,13 @@
         <v>2025</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>59</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H63" s="55">
         <v>28750953</v>
@@ -8554,9 +8453,7 @@
         <f t="shared" si="0"/>
         <v>28750953</v>
       </c>
-      <c r="L63" s="34">
-        <v>45810</v>
-      </c>
+      <c r="L63" s="34"/>
       <c r="M63" s="40">
         <v>28750953</v>
       </c>
@@ -8616,7 +8513,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C64" s="4">
         <v>45827</v>
@@ -8628,10 +8525,10 @@
         <v>28</v>
       </c>
       <c r="F64" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="G64" s="13" t="s">
         <v>282</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>283</v>
       </c>
       <c r="H64" s="55">
         <v>24570024</v>
@@ -8646,9 +8543,7 @@
         <f t="shared" si="0"/>
         <v>30000000</v>
       </c>
-      <c r="L64" s="34">
-        <v>45840</v>
-      </c>
+      <c r="L64" s="34"/>
       <c r="M64" s="40">
         <v>0</v>
       </c>
@@ -8710,7 +8605,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C65" s="4">
         <v>45827</v>
@@ -8722,10 +8617,10 @@
         <v>42</v>
       </c>
       <c r="F65" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="G65" s="13" t="s">
         <v>285</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>286</v>
       </c>
       <c r="H65" s="55">
         <v>281640000</v>
@@ -8740,9 +8635,7 @@
         <f t="shared" si="0"/>
         <v>312620400</v>
       </c>
-      <c r="L65" s="34">
-        <v>45859</v>
-      </c>
+      <c r="L65" s="34"/>
       <c r="M65" s="40">
         <v>0</v>
       </c>
@@ -8804,7 +8697,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C66" s="4">
         <v>45828</v>
@@ -8819,7 +8712,7 @@
         <v>244</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H66" s="55">
         <v>49904186</v>
@@ -8834,9 +8727,7 @@
         <f t="shared" si="0"/>
         <v>55393646</v>
       </c>
-      <c r="L66" s="34">
-        <v>45859</v>
-      </c>
+      <c r="L66" s="34"/>
       <c r="M66" s="40">
         <v>0</v>
       </c>
@@ -8898,7 +8789,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C67" s="4">
         <v>45833</v>
@@ -8910,10 +8801,10 @@
         <v>28</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H67" s="55">
         <v>199017200</v>
@@ -8928,9 +8819,7 @@
         <f t="shared" si="0"/>
         <v>243000000</v>
       </c>
-      <c r="L67" s="34">
-        <v>45840</v>
-      </c>
+      <c r="L67" s="34"/>
       <c r="M67" s="40">
         <v>0</v>
       </c>
@@ -8992,7 +8881,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C68" s="4">
         <v>45845</v>
@@ -9001,13 +8890,13 @@
         <v>2025</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H68" s="55">
         <v>12158989</v>
@@ -9022,9 +8911,7 @@
         <f t="shared" si="0"/>
         <v>12158989</v>
       </c>
-      <c r="L68" s="34">
-        <v>45846</v>
-      </c>
+      <c r="L68" s="34"/>
       <c r="M68" s="40">
         <v>12158989</v>
       </c>
@@ -9084,7 +8971,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C69" s="4">
         <v>45845</v>
@@ -9093,13 +8980,13 @@
         <v>2025</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H69" s="55">
         <v>5349022</v>
@@ -9114,9 +9001,7 @@
         <f t="shared" ref="K69:K132" si="9">SUM(H69:J69)</f>
         <v>5349022</v>
       </c>
-      <c r="L69" s="34">
-        <v>45846</v>
-      </c>
+      <c r="L69" s="34"/>
       <c r="M69" s="40">
         <v>5349022</v>
       </c>
@@ -9176,7 +9061,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C70" s="4">
         <v>45845</v>
@@ -9185,13 +9070,13 @@
         <v>2025</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H70" s="55">
         <v>5349022</v>
@@ -9206,9 +9091,7 @@
         <f t="shared" si="9"/>
         <v>5349022</v>
       </c>
-      <c r="L70" s="34">
-        <v>45849</v>
-      </c>
+      <c r="L70" s="34"/>
       <c r="M70" s="40">
         <v>5349022</v>
       </c>
@@ -9268,7 +9151,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C71" s="4">
         <v>45845</v>
@@ -9277,13 +9160,13 @@
         <v>2025</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H71" s="55">
         <v>10698044</v>
@@ -9298,9 +9181,7 @@
         <f t="shared" si="9"/>
         <v>10698044</v>
       </c>
-      <c r="L71" s="34">
-        <v>45847</v>
-      </c>
+      <c r="L71" s="34"/>
       <c r="M71" s="40">
         <v>10698044</v>
       </c>
@@ -9360,7 +9241,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C72" s="4">
         <v>45845</v>
@@ -9369,13 +9250,13 @@
         <v>2025</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F72" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H72" s="55">
         <v>7775522</v>
@@ -9390,9 +9271,7 @@
         <f t="shared" si="9"/>
         <v>7775522</v>
       </c>
-      <c r="L72" s="34">
-        <v>45847</v>
-      </c>
+      <c r="L72" s="34"/>
       <c r="M72" s="40">
         <v>7775522</v>
       </c>
@@ -9452,7 +9331,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C73" s="4">
         <v>45845</v>
@@ -9461,13 +9340,13 @@
         <v>2025</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H73" s="55">
         <v>7775522</v>
@@ -9482,9 +9361,7 @@
         <f t="shared" si="9"/>
         <v>7775522</v>
       </c>
-      <c r="L73" s="34">
-        <v>45847</v>
-      </c>
+      <c r="L73" s="34"/>
       <c r="M73" s="40">
         <v>7775522</v>
       </c>
@@ -9544,7 +9421,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C74" s="4">
         <v>45859</v>
@@ -9556,10 +9433,10 @@
         <v>42</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G74" s="20" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H74" s="55">
         <v>30064660</v>
@@ -9574,9 +9451,7 @@
         <f t="shared" si="9"/>
         <v>33371773</v>
       </c>
-      <c r="L74" s="34">
-        <v>45891</v>
-      </c>
+      <c r="L74" s="34"/>
       <c r="M74" s="40">
         <v>0</v>
       </c>
@@ -9638,7 +9513,7 @@
         <v>71</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C75" s="4">
         <v>45860</v>
@@ -9647,13 +9522,13 @@
         <v>2025</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F75" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H75" s="55">
         <v>4500000</v>
@@ -9668,9 +9543,7 @@
         <f t="shared" si="9"/>
         <v>4500000</v>
       </c>
-      <c r="L75" s="34">
-        <v>45861</v>
-      </c>
+      <c r="L75" s="34"/>
       <c r="M75" s="40">
         <v>4500000</v>
       </c>
@@ -9730,7 +9603,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C76" s="4">
         <v>45862</v>
@@ -9739,13 +9612,13 @@
         <v>2025</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F76" s="13" t="s">
         <v>233</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H76" s="55">
         <v>5568158</v>
@@ -9760,9 +9633,7 @@
         <f t="shared" si="9"/>
         <v>5568158</v>
       </c>
-      <c r="L76" s="34">
-        <v>45863</v>
-      </c>
+      <c r="L76" s="34"/>
       <c r="M76" s="40">
         <v>5568158</v>
       </c>
@@ -9822,7 +9693,7 @@
         <v>73</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C77" s="4">
         <v>45870</v>
@@ -9834,10 +9705,10 @@
         <v>44</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H77" s="55">
         <v>421113514</v>
@@ -9852,9 +9723,7 @@
         <f t="shared" si="9"/>
         <v>514179601</v>
       </c>
-      <c r="L77" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L77" s="34"/>
       <c r="M77" s="40">
         <v>0</v>
       </c>
@@ -9916,7 +9785,7 @@
         <v>74</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C78" s="4">
         <v>45870</v>
@@ -9928,10 +9797,10 @@
         <v>46</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G78" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H78" s="55">
         <v>737100737</v>
@@ -9946,9 +9815,7 @@
         <f t="shared" si="9"/>
         <v>900000000</v>
       </c>
-      <c r="L78" s="34">
-        <v>45903</v>
-      </c>
+      <c r="L78" s="34"/>
       <c r="M78" s="40">
         <v>0</v>
       </c>
@@ -10010,7 +9877,7 @@
         <v>75</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C79" s="4">
         <v>45870</v>
@@ -10019,13 +9886,13 @@
         <v>2025</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H79" s="55">
         <v>619885941</v>
@@ -10040,9 +9907,7 @@
         <f t="shared" si="9"/>
         <v>750000000</v>
       </c>
-      <c r="L79" s="34">
-        <v>45889</v>
-      </c>
+      <c r="L79" s="34"/>
       <c r="M79" s="40">
         <v>0</v>
       </c>
@@ -10104,7 +9969,7 @@
         <v>76</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C80" s="4">
         <v>45887</v>
@@ -10116,10 +9981,10 @@
         <v>42</v>
       </c>
       <c r="F80" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H80" s="55">
         <v>63346343</v>
@@ -10134,9 +9999,7 @@
         <f t="shared" si="9"/>
         <v>70314441</v>
       </c>
-      <c r="L80" s="34">
-        <v>45917</v>
-      </c>
+      <c r="L80" s="34"/>
       <c r="M80" s="40">
         <v>0</v>
       </c>
@@ -10198,7 +10061,7 @@
         <v>77</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C81" s="4">
         <v>45936</v>
@@ -10210,10 +10073,10 @@
         <v>26</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H81" s="55">
         <v>727203036</v>
@@ -10228,9 +10091,7 @@
         <f t="shared" si="9"/>
         <v>871771000</v>
       </c>
-      <c r="L81" s="34">
-        <v>45968</v>
-      </c>
+      <c r="L81" s="34"/>
       <c r="M81" s="40">
         <v>0</v>
       </c>
@@ -10292,7 +10153,7 @@
         <v>78</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C82" s="4">
         <v>45901</v>
@@ -10304,10 +10165,10 @@
         <v>28</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H82" s="55">
         <v>475020475</v>
@@ -10322,9 +10183,7 @@
         <f t="shared" si="9"/>
         <v>580000000</v>
       </c>
-      <c r="L82" s="34">
-        <v>45919</v>
-      </c>
+      <c r="L82" s="34"/>
       <c r="M82" s="40">
         <v>0</v>
       </c>
@@ -10386,7 +10245,7 @@
         <v>79</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C83" s="4">
         <v>45902</v>
@@ -10398,10 +10257,10 @@
         <v>28</v>
       </c>
       <c r="F83" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="G83" s="20" t="s">
         <v>454</v>
-      </c>
-      <c r="G83" s="20" t="s">
-        <v>455</v>
       </c>
       <c r="H83" s="55">
         <v>211083682</v>
@@ -10416,9 +10275,7 @@
         <f t="shared" si="9"/>
         <v>257733176</v>
       </c>
-      <c r="L83" s="34">
-        <v>45923</v>
-      </c>
+      <c r="L83" s="34"/>
       <c r="M83" s="40">
         <v>0</v>
       </c>
@@ -10480,7 +10337,7 @@
         <v>80</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C84" s="4">
         <v>45902</v>
@@ -10492,10 +10349,10 @@
         <v>42</v>
       </c>
       <c r="F84" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="G84" s="20" t="s">
         <v>457</v>
-      </c>
-      <c r="G84" s="20" t="s">
-        <v>458</v>
       </c>
       <c r="H84" s="55">
         <v>37957708</v>
@@ -10510,9 +10367,7 @@
         <f t="shared" si="9"/>
         <v>45293035</v>
       </c>
-      <c r="L84" s="34">
-        <v>45931</v>
-      </c>
+      <c r="L84" s="34"/>
       <c r="M84" s="40">
         <v>0</v>
       </c>
@@ -10574,7 +10429,7 @@
         <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C85" s="4">
         <v>45911</v>
@@ -10586,10 +10441,10 @@
         <v>46</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H85" s="55">
         <v>245700246</v>
@@ -10604,9 +10459,7 @@
         <f t="shared" si="9"/>
         <v>300000000</v>
       </c>
-      <c r="L85" s="34">
-        <v>45915</v>
-      </c>
+      <c r="L85" s="34"/>
       <c r="M85" s="40">
         <v>0</v>
       </c>
@@ -10671,7 +10524,7 @@
         <v>82</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C86" s="4">
         <v>45911</v>
@@ -10683,10 +10536,10 @@
         <v>26</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H86" s="55">
         <v>186321738</v>
@@ -10701,9 +10554,7 @@
         <f t="shared" si="9"/>
         <v>223362500</v>
       </c>
-      <c r="L86" s="34">
-        <v>45923</v>
-      </c>
+      <c r="L86" s="34"/>
       <c r="M86" s="40">
         <v>0</v>
       </c>
@@ -10765,7 +10616,7 @@
         <v>83</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C87" s="4">
         <v>45916</v>
@@ -10777,10 +10628,10 @@
         <v>44</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H87" s="55">
         <v>252252252</v>
@@ -10795,9 +10646,7 @@
         <f t="shared" si="9"/>
         <v>280000000</v>
       </c>
-      <c r="L87" s="34">
-        <v>45933</v>
-      </c>
+      <c r="L87" s="34"/>
       <c r="M87" s="40">
         <v>0</v>
       </c>
@@ -10859,7 +10708,7 @@
         <v>84</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C88" s="4">
         <v>45918</v>
@@ -10871,10 +10720,10 @@
         <v>42</v>
       </c>
       <c r="F88" s="20" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H88" s="55">
         <v>58859523</v>
@@ -10889,9 +10738,7 @@
         <f t="shared" si="9"/>
         <v>65334071</v>
       </c>
-      <c r="L88" s="34">
-        <v>45947</v>
-      </c>
+      <c r="L88" s="34"/>
       <c r="M88" s="40">
         <v>0</v>
       </c>
@@ -10946,7 +10793,7 @@
         <v>0</v>
       </c>
       <c r="AD88" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="89" spans="1:31" s="21" customFormat="1">
@@ -10955,7 +10802,7 @@
         <v>85</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C89" s="4">
         <v>45945</v>
@@ -10967,10 +10814,10 @@
         <v>42</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H89" s="55">
         <v>26270047</v>
@@ -10985,9 +10832,7 @@
         <f t="shared" si="9"/>
         <v>30681419</v>
       </c>
-      <c r="L89" s="34">
-        <v>45982</v>
-      </c>
+      <c r="L89" s="34"/>
       <c r="M89" s="40">
         <v>0</v>
       </c>
@@ -11049,7 +10894,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C90" s="4">
         <v>45964</v>
@@ -11061,10 +10906,10 @@
         <v>26</v>
       </c>
       <c r="F90" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="G90" s="20" t="s">
         <v>509</v>
-      </c>
-      <c r="G90" s="20" t="s">
-        <v>510</v>
       </c>
       <c r="H90" s="55">
         <v>700996750</v>
@@ -11079,9 +10924,7 @@
         <f t="shared" si="9"/>
         <v>855917032</v>
       </c>
-      <c r="L90" s="34">
-        <v>45993</v>
-      </c>
+      <c r="L90" s="34"/>
       <c r="M90" s="40">
         <v>0</v>
       </c>
@@ -11143,7 +10986,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C91" s="67">
         <v>45960</v>
@@ -11152,13 +10995,13 @@
         <v>2025</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F91" s="20" t="s">
         <v>59</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H91" s="8">
         <v>7586640</v>
@@ -11173,9 +11016,7 @@
         <f t="shared" si="9"/>
         <v>7586640</v>
       </c>
-      <c r="L91" s="67">
-        <v>45957</v>
-      </c>
+      <c r="L91" s="67"/>
       <c r="M91" s="40">
         <v>7586640</v>
       </c>
@@ -11234,21 +11075,23 @@
         <f t="shared" si="12"/>
         <v>88</v>
       </c>
-      <c r="B92" s="3">
-        <v>216</v>
-      </c>
-      <c r="C92" s="4"/>
+      <c r="B92" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C92" s="4">
+        <v>45953</v>
+      </c>
       <c r="D92" s="24">
         <v>2025</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F92" s="20" t="s">
         <v>66</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H92" s="55">
         <v>2985000000</v>
@@ -11263,9 +11106,7 @@
         <f t="shared" si="9"/>
         <v>2985000000</v>
       </c>
-      <c r="L92" s="34">
-        <v>45860</v>
-      </c>
+      <c r="L92" s="34"/>
       <c r="M92" s="40">
         <v>2985000000</v>
       </c>
@@ -11325,7 +11166,7 @@
         <v>89</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C93" s="4">
         <v>46057</v>
@@ -11334,13 +11175,13 @@
         <v>2025</v>
       </c>
       <c r="E93" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="F93" s="20" t="s">
         <v>644</v>
       </c>
-      <c r="F93" s="20" t="s">
+      <c r="G93" s="20" t="s">
         <v>645</v>
-      </c>
-      <c r="G93" s="20" t="s">
-        <v>646</v>
       </c>
       <c r="H93" s="55">
         <v>84355056</v>
@@ -11416,7 +11257,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C94" s="4">
         <v>46013</v>
@@ -11431,7 +11272,7 @@
         <v>242</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H94" s="55">
         <v>128247024</v>
@@ -11510,7 +11351,7 @@
         <v>91</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C95" s="4">
         <v>46006</v>
@@ -11522,10 +11363,10 @@
         <v>28</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H95" s="40">
         <v>140700000</v>
@@ -11602,7 +11443,7 @@
         <v>92</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C96" s="4">
         <v>46002</v>
@@ -11614,10 +11455,10 @@
         <v>42</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G96" s="20" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H96" s="55">
         <v>40236000</v>
@@ -11694,7 +11535,7 @@
         <v>93</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C97" s="4">
         <v>46009</v>
@@ -11706,10 +11547,10 @@
         <v>28</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H97" s="55">
         <v>532350532</v>
@@ -11786,7 +11627,7 @@
         <v>94</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C98" s="4">
         <v>46009</v>
@@ -11798,10 +11639,10 @@
         <v>28</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H98" s="55">
         <v>409500410</v>
@@ -11878,7 +11719,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C99" s="4">
         <v>46009</v>
@@ -11890,10 +11731,10 @@
         <v>28</v>
       </c>
       <c r="F99" s="20" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H99" s="55">
         <v>655200655</v>
@@ -11970,7 +11811,7 @@
         <v>96</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C100" s="4">
         <v>45996</v>
@@ -11979,13 +11820,13 @@
         <v>2025</v>
       </c>
       <c r="E100" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="F100" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="G100" s="20" t="s">
         <v>590</v>
-      </c>
-      <c r="F100" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="G100" s="20" t="s">
-        <v>591</v>
       </c>
       <c r="H100" s="55">
         <v>910000</v>
@@ -12000,9 +11841,7 @@
         <f t="shared" si="9"/>
         <v>910000</v>
       </c>
-      <c r="L100" s="34">
-        <v>45922</v>
-      </c>
+      <c r="L100" s="34"/>
       <c r="M100" s="40">
         <v>910000</v>
       </c>
@@ -12064,37 +11903,37 @@
         <v>97</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C101" s="4"/>
-      <c r="D101" s="24" t="s">
-        <v>1</v>
+        <v>650</v>
+      </c>
+      <c r="C101" s="4">
+        <v>46097</v>
+      </c>
+      <c r="D101" s="24">
+        <v>2026</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="F101" s="20" t="s">
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="G101" s="20" t="s">
-        <v>1</v>
+        <v>649</v>
       </c>
       <c r="H101" s="54">
-        <v>0</v>
+        <v>196018396</v>
       </c>
       <c r="I101" s="40">
-        <v>0</v>
+        <v>3339160</v>
       </c>
       <c r="J101" s="40">
-        <v>0</v>
+        <v>21929331</v>
       </c>
       <c r="K101" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L101" s="34" t="s">
-        <v>1</v>
-      </c>
+        <v>221286887</v>
+      </c>
+      <c r="L101" s="34"/>
       <c r="M101" s="40">
         <v>0</v>
       </c>
@@ -12130,12 +11969,12 @@
       </c>
       <c r="X101" s="39">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>221286887</v>
       </c>
       <c r="Y101" s="39"/>
       <c r="Z101" s="23">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-21929331</v>
       </c>
       <c r="AA101" s="39">
         <v>0</v>
@@ -12154,7 +11993,7 @@
         <v>98</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C102" s="4">
         <v>46013</v>
@@ -12166,7 +12005,7 @@
         <v>42</v>
       </c>
       <c r="F102" s="21" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G102" s="20" t="s">
         <v>1</v>
@@ -12246,7 +12085,7 @@
         <v>99</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C103" s="4">
         <v>46013</v>
@@ -12258,7 +12097,7 @@
         <v>42</v>
       </c>
       <c r="F103" s="20" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G103" s="20" t="s">
         <v>1</v>
@@ -12338,7 +12177,7 @@
         <v>100</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C104" s="4">
         <v>46013</v>
@@ -12350,7 +12189,7 @@
         <v>42</v>
       </c>
       <c r="F104" s="20" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G104" s="20" t="s">
         <v>1</v>
@@ -12430,7 +12269,7 @@
         <v>101</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C105" s="4">
         <v>46001</v>
@@ -12442,10 +12281,10 @@
         <v>42</v>
       </c>
       <c r="F105" s="20" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H105" s="55">
         <v>57889046</v>
@@ -12460,9 +12299,7 @@
         <f t="shared" si="9"/>
         <v>67599339</v>
       </c>
-      <c r="L105" s="34" t="s">
-        <v>1</v>
-      </c>
+      <c r="L105" s="34"/>
       <c r="M105" s="40">
         <v>0</v>
       </c>
@@ -12524,7 +12361,7 @@
         <v>102</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C106" s="4">
         <v>45994</v>
@@ -12536,10 +12373,10 @@
         <v>42</v>
       </c>
       <c r="F106" s="20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H106" s="55">
         <v>25500000</v>
@@ -12554,9 +12391,7 @@
         <f t="shared" si="9"/>
         <v>31135500</v>
       </c>
-      <c r="L106" s="34" t="s">
-        <v>1</v>
-      </c>
+      <c r="L106" s="34"/>
       <c r="M106" s="40">
         <v>0</v>
       </c>
@@ -12618,7 +12453,7 @@
         <v>103</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C107" s="4">
         <v>46022</v>
@@ -12633,7 +12468,7 @@
         <v>242</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H107" s="54">
         <v>3465049</v>
@@ -12648,9 +12483,7 @@
         <f t="shared" si="9"/>
         <v>3465049</v>
       </c>
-      <c r="L107" s="34">
-        <v>45734</v>
-      </c>
+      <c r="L107" s="34"/>
       <c r="M107" s="40">
         <v>3465049</v>
       </c>
@@ -12712,7 +12545,7 @@
         <v>104</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C108" s="4">
         <v>45968</v>
@@ -12742,9 +12575,7 @@
         <f t="shared" si="9"/>
         <v>1110000000</v>
       </c>
-      <c r="L108" s="34">
-        <v>45986</v>
-      </c>
+      <c r="L108" s="34"/>
       <c r="M108" s="40">
         <v>0</v>
       </c>
@@ -12806,7 +12637,7 @@
         <v>105</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C109" s="4">
         <v>46007</v>
@@ -12818,7 +12649,7 @@
         <v>35</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G109" s="21" t="s">
         <v>1</v>
@@ -12898,7 +12729,7 @@
         <v>106</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C110" s="4">
         <v>45972</v>
@@ -12907,13 +12738,13 @@
         <v>2025</v>
       </c>
       <c r="E110" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F110" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="G110" s="21" t="s">
         <v>566</v>
-      </c>
-      <c r="F110" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="G110" s="21" t="s">
-        <v>567</v>
       </c>
       <c r="H110" s="55">
         <v>655200655</v>
@@ -12928,9 +12759,7 @@
         <f t="shared" si="9"/>
         <v>800000000</v>
       </c>
-      <c r="L110" s="34">
-        <v>45975</v>
-      </c>
+      <c r="L110" s="34"/>
       <c r="M110" s="40">
         <v>0</v>
       </c>
@@ -12992,7 +12821,7 @@
         <v>107</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C111" s="4">
         <v>45972</v>
@@ -13004,7 +12833,7 @@
         <v>42</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G111" s="21" t="s">
         <v>247</v>
@@ -13084,7 +12913,7 @@
         <v>108</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C112" s="4">
         <v>45972</v>
@@ -13093,13 +12922,13 @@
         <v>2025</v>
       </c>
       <c r="E112" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="F112" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="G112" s="21" t="s">
         <v>569</v>
-      </c>
-      <c r="F112" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="G112" s="21" t="s">
-        <v>570</v>
       </c>
       <c r="H112" s="55">
         <v>675675676</v>
@@ -13176,7 +13005,7 @@
         <v>109</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C113" s="4">
         <v>45974</v>
@@ -13268,7 +13097,7 @@
         <v>110</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C114" s="4">
         <v>45975</v>
@@ -13280,7 +13109,7 @@
         <v>26</v>
       </c>
       <c r="F114" s="20" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G114" s="21" t="s">
         <v>1</v>
@@ -13298,9 +13127,7 @@
         <f t="shared" si="9"/>
         <v>6734646190</v>
       </c>
-      <c r="L114" s="34">
-        <v>45994</v>
-      </c>
+      <c r="L114" s="34"/>
       <c r="M114" s="40">
         <v>0</v>
       </c>
@@ -13362,7 +13189,7 @@
         <v>111</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C115" s="4">
         <v>45975</v>
@@ -13377,7 +13204,7 @@
         <v>1</v>
       </c>
       <c r="G115" s="21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H115" s="55">
         <v>0</v>
@@ -13454,7 +13281,7 @@
         <v>112</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C116" s="4">
         <v>45979</v>
@@ -13484,9 +13311,7 @@
         <f t="shared" si="9"/>
         <v>244153602</v>
       </c>
-      <c r="L116" s="34">
-        <v>46008</v>
-      </c>
+      <c r="L116" s="34"/>
       <c r="M116" s="40">
         <v>0</v>
       </c>
@@ -13548,7 +13373,7 @@
         <v>113</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C117" s="4">
         <v>45979</v>
@@ -13560,10 +13385,10 @@
         <v>42</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G117" s="21" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H117" s="55">
         <v>51940430</v>
@@ -13640,7 +13465,7 @@
         <v>114</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C118" s="4">
         <v>45980</v>
@@ -13732,7 +13557,7 @@
         <v>115</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C119" s="4">
         <v>45981</v>
@@ -13741,13 +13566,13 @@
         <v>2025</v>
       </c>
       <c r="E119" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="F119" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="G119" s="21" t="s">
         <v>579</v>
-      </c>
-      <c r="F119" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="G119" s="21" t="s">
-        <v>580</v>
       </c>
       <c r="H119" s="55">
         <v>625625626</v>
@@ -13762,9 +13587,7 @@
         <f t="shared" si="9"/>
         <v>750000000</v>
       </c>
-      <c r="L119" s="34">
-        <v>45995</v>
-      </c>
+      <c r="L119" s="34"/>
       <c r="M119" s="40">
         <v>0</v>
       </c>
@@ -13826,7 +13649,7 @@
         <v>116</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C120" s="4">
         <v>46077</v>
@@ -13838,10 +13661,10 @@
         <v>42</v>
       </c>
       <c r="F120" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G120" s="21" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H120" s="55">
         <v>5355000</v>
@@ -13948,9 +13771,7 @@
         <f t="shared" si="9"/>
         <v>5550000</v>
       </c>
-      <c r="L121" s="34">
-        <v>45708</v>
-      </c>
+      <c r="L121" s="34"/>
       <c r="M121" s="40">
         <v>0</v>
       </c>
@@ -14042,9 +13863,7 @@
         <f t="shared" si="9"/>
         <v>5550000</v>
       </c>
-      <c r="L122" s="34">
-        <v>45693</v>
-      </c>
+      <c r="L122" s="34"/>
       <c r="M122" s="40">
         <v>0</v>
       </c>
@@ -14135,9 +13954,7 @@
         <f t="shared" si="9"/>
         <v>6216000</v>
       </c>
-      <c r="L123" s="34">
-        <v>45698</v>
-      </c>
+      <c r="L123" s="34"/>
       <c r="M123" s="40">
         <v>0</v>
       </c>
@@ -14228,9 +14045,7 @@
         <f t="shared" si="9"/>
         <v>6993000</v>
       </c>
-      <c r="L124" s="34">
-        <v>45709</v>
-      </c>
+      <c r="L124" s="34"/>
       <c r="M124" s="40">
         <v>0</v>
       </c>
@@ -14322,9 +14137,7 @@
         <f t="shared" si="9"/>
         <v>5772000</v>
       </c>
-      <c r="L125" s="34">
-        <v>45694</v>
-      </c>
+      <c r="L125" s="34"/>
       <c r="M125" s="40">
         <v>0</v>
       </c>
@@ -14415,9 +14228,7 @@
         <f t="shared" si="9"/>
         <v>5827500</v>
       </c>
-      <c r="L126" s="34">
-        <v>45708</v>
-      </c>
+      <c r="L126" s="34"/>
       <c r="M126" s="40">
         <v>0</v>
       </c>
@@ -14508,9 +14319,7 @@
         <f t="shared" si="9"/>
         <v>5550000</v>
       </c>
-      <c r="L127" s="34">
-        <v>45721</v>
-      </c>
+      <c r="L127" s="34"/>
       <c r="M127" s="40">
         <v>0</v>
       </c>
@@ -14601,9 +14410,7 @@
         <f t="shared" si="9"/>
         <v>5550000</v>
       </c>
-      <c r="L128" s="34">
-        <v>45783</v>
-      </c>
+      <c r="L128" s="34"/>
       <c r="M128" s="40">
         <v>0</v>
       </c>
@@ -14679,7 +14486,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="35" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H129" s="75">
         <v>0</v>
@@ -14786,9 +14593,7 @@
         <f t="shared" si="9"/>
         <v>787234517</v>
       </c>
-      <c r="L130" s="67">
-        <v>45779</v>
-      </c>
+      <c r="L130" s="67"/>
       <c r="M130" s="40">
         <v>0</v>
       </c>
@@ -14880,9 +14685,7 @@
         <f t="shared" si="9"/>
         <v>36920243</v>
       </c>
-      <c r="L131" s="34">
-        <v>45757</v>
-      </c>
+      <c r="L131" s="34"/>
       <c r="M131" s="40">
         <v>0</v>
       </c>
@@ -14959,7 +14762,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="35" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H132" s="75">
         <v>0</v>
@@ -15036,7 +14839,7 @@
         <v>129</v>
       </c>
       <c r="B133" s="77" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C133" s="79">
         <v>45798</v>
@@ -15051,7 +14854,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="35" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H133" s="75">
         <v>0</v>
@@ -15143,7 +14946,7 @@
         <v>1</v>
       </c>
       <c r="G134" s="35" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H134" s="75">
         <v>0</v>
@@ -15235,7 +15038,7 @@
         <v>1</v>
       </c>
       <c r="G135" s="35" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H135" s="75">
         <v>0</v>
@@ -15342,9 +15145,7 @@
         <f t="shared" si="21"/>
         <v>149488097</v>
       </c>
-      <c r="L136" s="67">
-        <v>45832</v>
-      </c>
+      <c r="L136" s="67"/>
       <c r="M136" s="40">
         <v>0</v>
       </c>
@@ -15436,9 +15237,7 @@
         <f t="shared" si="21"/>
         <v>9142665</v>
       </c>
-      <c r="L137" s="34">
-        <v>45768</v>
-      </c>
+      <c r="L137" s="34"/>
       <c r="M137" s="40">
         <v>0</v>
       </c>
@@ -15515,7 +15314,7 @@
         <v>1</v>
       </c>
       <c r="G138" s="35" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H138" s="75">
         <v>0</v>
@@ -15606,7 +15405,7 @@
         <v>1</v>
       </c>
       <c r="G139" s="35" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H139" s="75">
         <v>0</v>
@@ -15697,7 +15496,7 @@
         <v>1</v>
       </c>
       <c r="G140" s="35" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H140" s="75">
         <v>0</v>
@@ -15788,7 +15587,7 @@
         <v>1</v>
       </c>
       <c r="G141" s="35" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H141" s="75">
         <v>0</v>
@@ -15879,7 +15678,7 @@
         <v>1</v>
       </c>
       <c r="G142" s="35" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H142" s="75">
         <v>0</v>
@@ -15970,7 +15769,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="35" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H143" s="75">
         <v>0</v>
@@ -16061,7 +15860,7 @@
         <v>1</v>
       </c>
       <c r="G144" s="35" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H144" s="75">
         <v>0</v>
@@ -16167,9 +15966,7 @@
         <f t="shared" si="21"/>
         <v>50931834</v>
       </c>
-      <c r="L145" s="34">
-        <v>45763</v>
-      </c>
+      <c r="L145" s="34"/>
       <c r="M145" s="40">
         <v>0</v>
       </c>
@@ -16261,9 +16058,7 @@
         <f t="shared" si="21"/>
         <v>390802050</v>
       </c>
-      <c r="L146" s="34">
-        <v>45771</v>
-      </c>
+      <c r="L146" s="34"/>
       <c r="M146" s="40">
         <v>0</v>
       </c>
@@ -16318,7 +16113,7 @@
         <v>390028950</v>
       </c>
       <c r="AD146" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="147" spans="1:31" s="21" customFormat="1">
@@ -16357,9 +16152,7 @@
         <f t="shared" si="21"/>
         <v>17274108</v>
       </c>
-      <c r="L147" s="34">
-        <v>45771</v>
-      </c>
+      <c r="L147" s="34"/>
       <c r="M147" s="40">
         <v>0</v>
       </c>
@@ -16414,7 +16207,7 @@
         <v>17239936</v>
       </c>
       <c r="AD147" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="148" spans="1:31" s="21" customFormat="1">
@@ -16545,9 +16338,7 @@
         <f t="shared" si="21"/>
         <v>15300897</v>
       </c>
-      <c r="L149" s="34">
-        <v>45826</v>
-      </c>
+      <c r="L149" s="34"/>
       <c r="M149" s="40">
         <v>0</v>
       </c>
@@ -16701,7 +16492,7 @@
         <v>147</v>
       </c>
       <c r="B151" s="26" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C151" s="79">
         <v>45940</v>
@@ -16716,7 +16507,7 @@
         <v>1</v>
       </c>
       <c r="G151" s="35" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H151" s="75">
         <v>0</v>
@@ -16823,9 +16614,7 @@
         <f t="shared" si="21"/>
         <v>481950000</v>
       </c>
-      <c r="L152" s="34">
-        <v>45771</v>
-      </c>
+      <c r="L152" s="34"/>
       <c r="M152" s="40">
         <v>0</v>
       </c>
@@ -16880,7 +16669,7 @@
         <v>480996587</v>
       </c>
       <c r="AD152" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="153" spans="1:31" s="21" customFormat="1">
@@ -16889,7 +16678,7 @@
         <v>149</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C153" s="4">
         <v>45959</v>
@@ -16904,7 +16693,7 @@
         <v>74</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H153" s="55">
         <v>62907319</v>
@@ -16996,7 +16785,7 @@
         <v>1</v>
       </c>
       <c r="G154" s="35" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H154" s="75">
         <v>0</v>
@@ -17103,9 +16892,7 @@
         <f t="shared" si="21"/>
         <v>19792121</v>
       </c>
-      <c r="L155" s="34">
-        <v>45792</v>
-      </c>
+      <c r="L155" s="34"/>
       <c r="M155" s="40">
         <v>0</v>
       </c>
@@ -17185,7 +16972,7 @@
         <v>1</v>
       </c>
       <c r="G156" s="35" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H156" s="75">
         <v>0</v>
@@ -17292,9 +17079,7 @@
         <f t="shared" si="21"/>
         <v>52711125</v>
       </c>
-      <c r="L157" s="34">
-        <v>45785</v>
-      </c>
+      <c r="L157" s="34"/>
       <c r="M157" s="40">
         <v>0</v>
       </c>
@@ -17349,7 +17134,7 @@
         <v>52606850</v>
       </c>
       <c r="AD157" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="158" spans="1:31" s="21" customFormat="1">
@@ -17388,9 +17173,7 @@
         <f t="shared" si="21"/>
         <v>206550000</v>
       </c>
-      <c r="L158" s="34">
-        <v>45785</v>
-      </c>
+      <c r="L158" s="34"/>
       <c r="M158" s="40">
         <v>0</v>
       </c>
@@ -17445,7 +17228,7 @@
         <v>206141395</v>
       </c>
       <c r="AD158" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="159" spans="1:31" s="21" customFormat="1">
@@ -17469,7 +17252,7 @@
         <v>1</v>
       </c>
       <c r="G159" s="35" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H159" s="75">
         <v>0</v>
@@ -17539,7 +17322,7 @@
         <v>0</v>
       </c>
       <c r="AD159" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="160" spans="1:31" s="21" customFormat="1">
@@ -17563,7 +17346,7 @@
         <v>1</v>
       </c>
       <c r="G160" s="35" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H160" s="75">
         <v>0</v>
@@ -17670,9 +17453,7 @@
         <f t="shared" si="21"/>
         <v>80888594</v>
       </c>
-      <c r="L161" s="34">
-        <v>45799</v>
-      </c>
+      <c r="L161" s="34"/>
       <c r="M161" s="40">
         <v>0</v>
       </c>
@@ -17727,7 +17508,7 @@
         <v>80728577</v>
       </c>
       <c r="AD161" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AE161" s="31" t="s">
         <v>1</v>
@@ -17769,9 +17550,7 @@
         <f t="shared" si="21"/>
         <v>71174400</v>
       </c>
-      <c r="L162" s="34">
-        <v>45799</v>
-      </c>
+      <c r="L162" s="34"/>
       <c r="M162" s="40">
         <v>0</v>
       </c>
@@ -17826,7 +17605,7 @@
         <v>71033600</v>
       </c>
       <c r="AD162" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AE162" s="31" t="s">
         <v>1</v>
@@ -17868,9 +17647,7 @@
         <f t="shared" si="21"/>
         <v>11626500</v>
       </c>
-      <c r="L163" s="34">
-        <v>45799</v>
-      </c>
+      <c r="L163" s="34"/>
       <c r="M163" s="40">
         <v>0</v>
       </c>
@@ -17925,7 +17702,7 @@
         <v>11603500</v>
       </c>
       <c r="AD163" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AE163" s="31" t="s">
         <v>1</v>
@@ -17967,9 +17744,7 @@
         <f t="shared" si="21"/>
         <v>8007111</v>
       </c>
-      <c r="L164" s="34">
-        <v>45803</v>
-      </c>
+      <c r="L164" s="34"/>
       <c r="M164" s="40">
         <v>0</v>
       </c>
@@ -18024,7 +17799,7 @@
         <v>8007111</v>
       </c>
       <c r="AD164" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AE164" s="31" t="s">
         <v>1</v>
@@ -18066,9 +17841,7 @@
         <f t="shared" si="21"/>
         <v>11631353</v>
       </c>
-      <c r="L165" s="34">
-        <v>45803</v>
-      </c>
+      <c r="L165" s="34"/>
       <c r="M165" s="40">
         <v>0</v>
       </c>
@@ -18123,7 +17896,7 @@
         <v>11631353</v>
       </c>
       <c r="AD165" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166" spans="1:31" s="21" customFormat="1">
@@ -18162,9 +17935,7 @@
         <f t="shared" si="21"/>
         <v>15257446</v>
       </c>
-      <c r="L166" s="34">
-        <v>45803</v>
-      </c>
+      <c r="L166" s="34"/>
       <c r="M166" s="40">
         <v>0</v>
       </c>
@@ -18219,7 +17990,7 @@
         <v>15257446</v>
       </c>
       <c r="AD166" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="167" spans="1:31" s="21" customFormat="1">
@@ -18258,9 +18029,7 @@
         <f t="shared" si="21"/>
         <v>12194480</v>
       </c>
-      <c r="L167" s="34">
-        <v>45803</v>
-      </c>
+      <c r="L167" s="34"/>
       <c r="M167" s="40">
         <v>0</v>
       </c>
@@ -18315,7 +18084,7 @@
         <v>12194480</v>
       </c>
       <c r="AD167" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="168" spans="1:31" s="21" customFormat="1">
@@ -18324,7 +18093,7 @@
         <v>164</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C168" s="4">
         <v>45793</v>
@@ -18339,7 +18108,7 @@
         <v>74</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H168" s="55">
         <v>5753850</v>
@@ -18354,9 +18123,7 @@
         <f t="shared" si="21"/>
         <v>6398857</v>
       </c>
-      <c r="L168" s="34">
-        <v>45880</v>
-      </c>
+      <c r="L168" s="34"/>
       <c r="M168" s="40">
         <v>0</v>
       </c>
@@ -18418,7 +18185,7 @@
         <v>165</v>
       </c>
       <c r="B169" s="26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C169" s="79">
         <v>45825</v>
@@ -18433,7 +18200,7 @@
         <v>1</v>
       </c>
       <c r="G169" s="35" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H169" s="75">
         <v>0</v>
@@ -18510,7 +18277,7 @@
         <v>166</v>
       </c>
       <c r="B170" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C170" s="79">
         <v>45737</v>
@@ -18525,7 +18292,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="35" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H170" s="75">
         <v>0</v>
@@ -18602,7 +18369,7 @@
         <v>167</v>
       </c>
       <c r="B171" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C171" s="79">
         <v>45740</v>
@@ -18617,7 +18384,7 @@
         <v>1</v>
       </c>
       <c r="G171" s="35" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H171" s="75">
         <v>0</v>
@@ -18694,7 +18461,7 @@
         <v>168</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C172" s="4">
         <v>45810</v>
@@ -18709,7 +18476,7 @@
         <v>233</v>
       </c>
       <c r="G172" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H172" s="55">
         <v>648783383</v>
@@ -18724,9 +18491,7 @@
         <f t="shared" si="21"/>
         <v>655920000</v>
       </c>
-      <c r="L172" s="34">
-        <v>45818</v>
-      </c>
+      <c r="L172" s="34"/>
       <c r="M172" s="40">
         <v>0</v>
       </c>
@@ -18788,7 +18553,7 @@
         <v>169</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C173" s="4">
         <v>45811</v>
@@ -18797,13 +18562,13 @@
         <v>2025</v>
       </c>
       <c r="E173" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F173" s="20" t="s">
         <v>69</v>
       </c>
       <c r="G173" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H173" s="55">
         <v>1900000</v>
@@ -18818,9 +18583,7 @@
         <f t="shared" si="21"/>
         <v>1920900</v>
       </c>
-      <c r="L173" s="34">
-        <v>45918</v>
-      </c>
+      <c r="L173" s="34"/>
       <c r="M173" s="40">
         <v>0</v>
       </c>
@@ -18881,7 +18644,7 @@
         <v>170</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C174" s="4">
         <v>45811</v>
@@ -18890,13 +18653,13 @@
         <v>2025</v>
       </c>
       <c r="E174" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F174" s="20" t="s">
         <v>69</v>
       </c>
       <c r="G174" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H174" s="55">
         <v>12800000</v>
@@ -18911,9 +18674,7 @@
         <f t="shared" si="21"/>
         <v>12940800</v>
       </c>
-      <c r="L174" s="34">
-        <v>45839</v>
-      </c>
+      <c r="L174" s="34"/>
       <c r="M174" s="40">
         <v>0</v>
       </c>
@@ -18974,7 +18735,7 @@
         <v>171</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C175" s="4">
         <v>45811</v>
@@ -18983,13 +18744,13 @@
         <v>2025</v>
       </c>
       <c r="E175" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F175" s="20" t="s">
         <v>69</v>
       </c>
       <c r="G175" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H175" s="55">
         <v>12800000</v>
@@ -19004,9 +18765,7 @@
         <f t="shared" si="21"/>
         <v>12940800</v>
       </c>
-      <c r="L175" s="34">
-        <v>45833</v>
-      </c>
+      <c r="L175" s="34"/>
       <c r="M175" s="40">
         <v>0</v>
       </c>
@@ -19067,7 +18826,7 @@
         <v>172</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C176" s="4">
         <v>45811</v>
@@ -19076,13 +18835,13 @@
         <v>2025</v>
       </c>
       <c r="E176" s="20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F176" s="20" t="s">
         <v>69</v>
       </c>
       <c r="G176" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H176" s="55">
         <v>12800000</v>
@@ -19097,9 +18856,7 @@
         <f t="shared" si="21"/>
         <v>12940800</v>
       </c>
-      <c r="L176" s="34">
-        <v>45856</v>
-      </c>
+      <c r="L176" s="34"/>
       <c r="M176" s="40">
         <v>0</v>
       </c>
@@ -19160,7 +18917,7 @@
         <v>173</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C177" s="4">
         <v>45824</v>
@@ -19175,7 +18932,7 @@
         <v>233</v>
       </c>
       <c r="G177" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H177" s="55">
         <v>324391691</v>
@@ -19190,9 +18947,7 @@
         <f t="shared" si="21"/>
         <v>327960000</v>
       </c>
-      <c r="L177" s="34">
-        <v>45833</v>
-      </c>
+      <c r="L177" s="34"/>
       <c r="M177" s="40">
         <v>0</v>
       </c>
@@ -19254,7 +19009,7 @@
         <v>174</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C178" s="4">
         <v>45838</v>
@@ -19269,7 +19024,7 @@
         <v>233</v>
       </c>
       <c r="G178" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H178" s="55">
         <v>108131553</v>
@@ -19284,9 +19039,7 @@
         <f t="shared" si="21"/>
         <v>109321000</v>
       </c>
-      <c r="L178" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L178" s="34"/>
       <c r="M178" s="40">
         <v>0</v>
       </c>
@@ -19348,7 +19101,7 @@
         <v>175</v>
       </c>
       <c r="B179" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C179" s="79">
         <v>45842</v>
@@ -19363,7 +19116,7 @@
         <v>1</v>
       </c>
       <c r="G179" s="35" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H179" s="75">
         <v>0</v>
@@ -19445,7 +19198,7 @@
         <v>176</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C180" s="4">
         <v>45845</v>
@@ -19460,7 +19213,7 @@
         <v>233</v>
       </c>
       <c r="G180" s="20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H180" s="55">
         <v>8234580</v>
@@ -19475,9 +19228,7 @@
         <f t="shared" si="21"/>
         <v>8325160</v>
       </c>
-      <c r="L180" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L180" s="34"/>
       <c r="M180" s="40">
         <v>0</v>
       </c>
@@ -19531,7 +19282,7 @@
         <v>8325160</v>
       </c>
       <c r="AD180" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="181" spans="1:31" s="21" customFormat="1">
@@ -19540,7 +19291,7 @@
         <v>177</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C181" s="4">
         <v>45845</v>
@@ -19555,7 +19306,7 @@
         <v>233</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H181" s="55">
         <v>22632818</v>
@@ -19570,9 +19321,7 @@
         <f t="shared" si="21"/>
         <v>22881779</v>
       </c>
-      <c r="L181" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L181" s="34"/>
       <c r="M181" s="40">
         <v>0</v>
       </c>
@@ -19626,7 +19375,7 @@
         <v>22881779</v>
       </c>
       <c r="AD181" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="182" spans="1:31" s="21" customFormat="1">
@@ -19635,7 +19384,7 @@
         <v>178</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C182" s="4">
         <v>45845</v>
@@ -19650,7 +19399,7 @@
         <v>233</v>
       </c>
       <c r="G182" s="20" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H182" s="55">
         <v>1326500</v>
@@ -19665,9 +19414,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L182" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L182" s="34"/>
       <c r="M182" s="40">
         <v>0</v>
       </c>
@@ -19721,7 +19468,7 @@
         <v>1341092</v>
       </c>
       <c r="AD182" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="183" spans="1:31" s="21" customFormat="1">
@@ -19730,7 +19477,7 @@
         <v>179</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C183" s="4">
         <v>45845</v>
@@ -19745,7 +19492,7 @@
         <v>233</v>
       </c>
       <c r="G183" s="20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H183" s="55">
         <v>1326500</v>
@@ -19760,9 +19507,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L183" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L183" s="34"/>
       <c r="M183" s="40">
         <v>0</v>
       </c>
@@ -19816,7 +19561,7 @@
         <v>1341092</v>
       </c>
       <c r="AD183" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="184" spans="1:31" s="21" customFormat="1">
@@ -19825,7 +19570,7 @@
         <v>180</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C184" s="4">
         <v>45845</v>
@@ -19840,7 +19585,7 @@
         <v>233</v>
       </c>
       <c r="G184" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H184" s="55">
         <v>2653000</v>
@@ -19855,9 +19600,7 @@
         <f t="shared" si="21"/>
         <v>2682183</v>
       </c>
-      <c r="L184" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L184" s="34"/>
       <c r="M184" s="40">
         <v>0</v>
       </c>
@@ -19911,7 +19654,7 @@
         <v>2682183</v>
       </c>
       <c r="AD184" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="185" spans="1:31" s="21" customFormat="1">
@@ -19920,7 +19663,7 @@
         <v>181</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C185" s="4">
         <v>45845</v>
@@ -19935,7 +19678,7 @@
         <v>233</v>
       </c>
       <c r="G185" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H185" s="55">
         <v>1326500</v>
@@ -19950,9 +19693,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L185" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L185" s="34"/>
       <c r="M185" s="40">
         <v>0</v>
       </c>
@@ -20006,7 +19747,7 @@
         <v>1341092</v>
       </c>
       <c r="AD185" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="186" spans="1:31" s="21" customFormat="1">
@@ -20015,7 +19756,7 @@
         <v>182</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C186" s="4">
         <v>45845</v>
@@ -20030,7 +19771,7 @@
         <v>233</v>
       </c>
       <c r="G186" s="20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H186" s="55">
         <v>1326500</v>
@@ -20045,9 +19786,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L186" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L186" s="34"/>
       <c r="M186" s="40">
         <v>0</v>
       </c>
@@ -20101,7 +19840,7 @@
         <v>1341092</v>
       </c>
       <c r="AD186" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="187" spans="1:31" s="21" customFormat="1">
@@ -20110,7 +19849,7 @@
         <v>183</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C187" s="4">
         <v>45845</v>
@@ -20125,7 +19864,7 @@
         <v>233</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H187" s="55">
         <v>1326500</v>
@@ -20140,9 +19879,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L187" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L187" s="34"/>
       <c r="M187" s="40">
         <v>0</v>
       </c>
@@ -20196,7 +19933,7 @@
         <v>1341092</v>
       </c>
       <c r="AD187" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="188" spans="1:31" s="21" customFormat="1">
@@ -20205,7 +19942,7 @@
         <v>184</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C188" s="4">
         <v>45845</v>
@@ -20220,7 +19957,7 @@
         <v>233</v>
       </c>
       <c r="G188" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H188" s="55">
         <v>1326500</v>
@@ -20235,9 +19972,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L188" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L188" s="34"/>
       <c r="M188" s="40">
         <v>0</v>
       </c>
@@ -20291,7 +20026,7 @@
         <v>1341092</v>
       </c>
       <c r="AD188" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="189" spans="1:31" s="21" customFormat="1">
@@ -20300,7 +20035,7 @@
         <v>185</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C189" s="4">
         <v>45845</v>
@@ -20315,7 +20050,7 @@
         <v>233</v>
       </c>
       <c r="G189" s="20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H189" s="55">
         <v>1326500</v>
@@ -20330,9 +20065,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L189" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L189" s="34"/>
       <c r="M189" s="40">
         <v>0</v>
       </c>
@@ -20386,7 +20119,7 @@
         <v>1341092</v>
       </c>
       <c r="AD189" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="190" spans="1:31" s="76" customFormat="1">
@@ -20395,7 +20128,7 @@
         <v>186</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C190" s="4">
         <v>45845</v>
@@ -20410,7 +20143,7 @@
         <v>233</v>
       </c>
       <c r="G190" s="20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H190" s="55">
         <v>1326500</v>
@@ -20425,9 +20158,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L190" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L190" s="34"/>
       <c r="M190" s="40">
         <v>0</v>
       </c>
@@ -20481,7 +20212,7 @@
         <v>1341092</v>
       </c>
       <c r="AD190" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="191" spans="1:31" s="21" customFormat="1">
@@ -20490,7 +20221,7 @@
         <v>187</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C191" s="4">
         <v>45845</v>
@@ -20505,7 +20236,7 @@
         <v>233</v>
       </c>
       <c r="G191" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H191" s="55">
         <v>1326500</v>
@@ -20520,9 +20251,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L191" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L191" s="34"/>
       <c r="M191" s="40">
         <v>0</v>
       </c>
@@ -20576,7 +20305,7 @@
         <v>1341092</v>
       </c>
       <c r="AD191" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="192" spans="1:31" s="21" customFormat="1">
@@ -20585,7 +20314,7 @@
         <v>188</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C192" s="4">
         <v>45845</v>
@@ -20600,7 +20329,7 @@
         <v>233</v>
       </c>
       <c r="G192" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H192" s="55">
         <v>1326500</v>
@@ -20615,9 +20344,7 @@
         <f t="shared" si="21"/>
         <v>1341092</v>
       </c>
-      <c r="L192" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L192" s="34"/>
       <c r="M192" s="40">
         <v>0</v>
       </c>
@@ -20671,7 +20398,7 @@
         <v>1341092</v>
       </c>
       <c r="AD192" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="193" spans="1:31" s="21" customFormat="1">
@@ -20680,7 +20407,7 @@
         <v>189</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C193" s="4">
         <v>45845</v>
@@ -20695,7 +20422,7 @@
         <v>233</v>
       </c>
       <c r="G193" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H193" s="55">
         <v>6400860</v>
@@ -20710,9 +20437,7 @@
         <f t="shared" si="21"/>
         <v>6471269</v>
       </c>
-      <c r="L193" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L193" s="34"/>
       <c r="M193" s="40">
         <v>0</v>
       </c>
@@ -20766,7 +20491,7 @@
         <v>6471269</v>
       </c>
       <c r="AD193" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="194" spans="1:31" s="21" customFormat="1">
@@ -20775,7 +20500,7 @@
         <v>190</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C194" s="4">
         <v>45845</v>
@@ -20790,7 +20515,7 @@
         <v>233</v>
       </c>
       <c r="G194" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H194" s="55">
         <v>1200430</v>
@@ -20805,9 +20530,7 @@
         <f t="shared" si="21"/>
         <v>1213635</v>
       </c>
-      <c r="L194" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L194" s="34"/>
       <c r="M194" s="40">
         <v>0</v>
       </c>
@@ -20861,7 +20584,7 @@
         <v>1213635</v>
       </c>
       <c r="AD194" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="195" spans="1:31" s="21" customFormat="1">
@@ -20870,7 +20593,7 @@
         <v>191</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C195" s="4">
         <v>45845</v>
@@ -20885,7 +20608,7 @@
         <v>233</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H195" s="55">
         <v>1200430</v>
@@ -20900,9 +20623,7 @@
         <f t="shared" si="21"/>
         <v>1213635</v>
       </c>
-      <c r="L195" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L195" s="34"/>
       <c r="M195" s="40">
         <v>0</v>
       </c>
@@ -20956,7 +20677,7 @@
         <v>1213635</v>
       </c>
       <c r="AD195" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="196" spans="1:31" s="21" customFormat="1">
@@ -20965,7 +20686,7 @@
         <v>192</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C196" s="4">
         <v>45845</v>
@@ -20980,7 +20701,7 @@
         <v>233</v>
       </c>
       <c r="G196" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H196" s="55">
         <v>1200430</v>
@@ -20995,9 +20716,7 @@
         <f t="shared" si="21"/>
         <v>1213635</v>
       </c>
-      <c r="L196" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L196" s="34"/>
       <c r="M196" s="40">
         <v>0</v>
       </c>
@@ -21051,7 +20770,7 @@
         <v>1213635</v>
       </c>
       <c r="AD196" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="197" spans="1:31" s="21" customFormat="1">
@@ -21060,7 +20779,7 @@
         <v>193</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C197" s="4">
         <v>45845</v>
@@ -21075,7 +20794,7 @@
         <v>233</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H197" s="55">
         <v>2588534</v>
@@ -21090,9 +20809,7 @@
         <f t="shared" ref="K197:K260" si="31">SUM(H197:J197)</f>
         <v>2617008</v>
       </c>
-      <c r="L197" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L197" s="34"/>
       <c r="M197" s="40">
         <v>0</v>
       </c>
@@ -21146,7 +20863,7 @@
         <v>2617008</v>
       </c>
       <c r="AD197" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AE197" s="21" t="s">
         <v>1</v>
@@ -21158,7 +20875,7 @@
         <v>194</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C198" s="4">
         <v>45845</v>
@@ -21173,7 +20890,7 @@
         <v>233</v>
       </c>
       <c r="G198" s="20" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H198" s="55">
         <v>9249022</v>
@@ -21188,9 +20905,7 @@
         <f t="shared" si="31"/>
         <v>9350761</v>
       </c>
-      <c r="L198" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L198" s="34"/>
       <c r="M198" s="40">
         <v>0</v>
       </c>
@@ -21244,7 +20959,7 @@
         <v>9350761</v>
       </c>
       <c r="AD198" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="199" spans="1:31" s="21" customFormat="1">
@@ -21253,7 +20968,7 @@
         <v>195</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C199" s="4">
         <v>45845</v>
@@ -21268,7 +20983,7 @@
         <v>233</v>
       </c>
       <c r="G199" s="20" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H199" s="55">
         <v>1800000</v>
@@ -21283,9 +20998,7 @@
         <f t="shared" si="31"/>
         <v>1819800</v>
       </c>
-      <c r="L199" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L199" s="34"/>
       <c r="M199" s="40">
         <v>0</v>
       </c>
@@ -21339,7 +21052,7 @@
         <v>1819800</v>
       </c>
       <c r="AD199" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="200" spans="1:31" s="21" customFormat="1">
@@ -21348,7 +21061,7 @@
         <v>196</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C200" s="4">
         <v>45845</v>
@@ -21363,7 +21076,7 @@
         <v>233</v>
       </c>
       <c r="G200" s="20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H200" s="55">
         <v>26941560</v>
@@ -21378,9 +21091,7 @@
         <f t="shared" si="31"/>
         <v>27237917</v>
       </c>
-      <c r="L200" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L200" s="34"/>
       <c r="M200" s="40">
         <v>0</v>
       </c>
@@ -21434,7 +21145,7 @@
         <v>27237917</v>
       </c>
       <c r="AD200" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="201" spans="1:31" s="21" customFormat="1">
@@ -21443,7 +21154,7 @@
         <v>197</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C201" s="4">
         <v>45845</v>
@@ -21458,7 +21169,7 @@
         <v>233</v>
       </c>
       <c r="G201" s="20" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H201" s="55">
         <v>4701311</v>
@@ -21473,9 +21184,7 @@
         <f t="shared" si="31"/>
         <v>4753025</v>
       </c>
-      <c r="L201" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L201" s="34"/>
       <c r="M201" s="40">
         <v>0</v>
       </c>
@@ -21529,7 +21238,7 @@
         <v>4753025</v>
       </c>
       <c r="AD201" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="202" spans="1:31" s="21" customFormat="1">
@@ -21538,7 +21247,7 @@
         <v>198</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C202" s="4">
         <v>45845</v>
@@ -21553,7 +21262,7 @@
         <v>233</v>
       </c>
       <c r="G202" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H202" s="55">
         <v>4701311</v>
@@ -21568,9 +21277,7 @@
         <f t="shared" si="31"/>
         <v>4753025</v>
       </c>
-      <c r="L202" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L202" s="34"/>
       <c r="M202" s="40">
         <v>0</v>
       </c>
@@ -21624,7 +21331,7 @@
         <v>4753025</v>
       </c>
       <c r="AD202" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="203" spans="1:31" s="21" customFormat="1">
@@ -21633,7 +21340,7 @@
         <v>199</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C203" s="4">
         <v>45845</v>
@@ -21648,7 +21355,7 @@
         <v>233</v>
       </c>
       <c r="G203" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H203" s="55">
         <v>3809967</v>
@@ -21663,9 +21370,7 @@
         <f t="shared" si="31"/>
         <v>3851877</v>
       </c>
-      <c r="L203" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L203" s="34"/>
       <c r="M203" s="40">
         <v>0</v>
       </c>
@@ -21719,7 +21424,7 @@
         <v>3851877</v>
       </c>
       <c r="AD203" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="204" spans="1:31" s="21" customFormat="1">
@@ -21728,7 +21433,7 @@
         <v>200</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C204" s="4">
         <v>45845</v>
@@ -21743,7 +21448,7 @@
         <v>233</v>
       </c>
       <c r="G204" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H204" s="55">
         <v>3809967</v>
@@ -21758,9 +21463,7 @@
         <f t="shared" si="31"/>
         <v>3851877</v>
       </c>
-      <c r="L204" s="34">
-        <v>45848</v>
-      </c>
+      <c r="L204" s="34"/>
       <c r="M204" s="40">
         <v>0</v>
       </c>
@@ -21814,7 +21517,7 @@
         <v>3851877</v>
       </c>
       <c r="AD204" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="205" spans="1:31" s="21" customFormat="1">
@@ -21823,7 +21526,7 @@
         <v>201</v>
       </c>
       <c r="B205" s="26" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C205" s="79">
         <v>45721</v>
@@ -21838,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="G205" s="35" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H205" s="75">
         <v>0</v>
@@ -21915,7 +21618,7 @@
         <v>202</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C206" s="4">
         <v>45848</v>
@@ -21927,10 +21630,10 @@
         <v>192</v>
       </c>
       <c r="F206" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G206" s="20" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H206" s="55">
         <v>105119540</v>
@@ -21945,9 +21648,7 @@
         <f t="shared" si="31"/>
         <v>116903440</v>
       </c>
-      <c r="L206" s="34">
-        <v>45929</v>
-      </c>
+      <c r="L206" s="34"/>
       <c r="M206" s="40">
         <v>0</v>
       </c>
@@ -22009,7 +21710,7 @@
         <v>203</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C207" s="4">
         <v>45860</v>
@@ -22024,7 +21725,7 @@
         <v>233</v>
       </c>
       <c r="G207" s="20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H207" s="55">
         <v>30000000</v>
@@ -22039,9 +21740,7 @@
         <f t="shared" si="31"/>
         <v>30330000</v>
       </c>
-      <c r="L207" s="34">
-        <v>45863</v>
-      </c>
+      <c r="L207" s="34"/>
       <c r="M207" s="40">
         <v>0</v>
       </c>
@@ -22096,7 +21795,7 @@
         <v>29730000</v>
       </c>
       <c r="AD207" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="208" spans="1:31" s="21" customFormat="1">
@@ -22105,7 +21804,7 @@
         <v>204</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C208" s="4">
         <v>45860</v>
@@ -22120,7 +21819,7 @@
         <v>233</v>
       </c>
       <c r="G208" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H208" s="55">
         <v>26200000</v>
@@ -22135,9 +21834,7 @@
         <f t="shared" si="31"/>
         <v>26488200</v>
       </c>
-      <c r="L208" s="34">
-        <v>45863</v>
-      </c>
+      <c r="L208" s="34"/>
       <c r="M208" s="40">
         <v>0</v>
       </c>
@@ -22192,7 +21889,7 @@
         <v>25964200</v>
       </c>
       <c r="AD208" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="209" spans="1:31" s="76" customFormat="1">
@@ -22201,7 +21898,7 @@
         <v>205</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C209" s="4">
         <v>45860</v>
@@ -22216,7 +21913,7 @@
         <v>233</v>
       </c>
       <c r="G209" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H209" s="55">
         <v>67400000</v>
@@ -22231,9 +21928,7 @@
         <f t="shared" si="31"/>
         <v>68141400</v>
       </c>
-      <c r="L209" s="34">
-        <v>45863</v>
-      </c>
+      <c r="L209" s="34"/>
       <c r="M209" s="40">
         <v>0</v>
       </c>
@@ -22288,7 +21983,7 @@
         <v>66793400</v>
       </c>
       <c r="AD209" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="210" spans="1:31" s="21" customFormat="1">
@@ -22297,7 +21992,7 @@
         <v>206</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C210" s="4">
         <v>45870</v>
@@ -22306,13 +22001,13 @@
         <v>2025</v>
       </c>
       <c r="E210" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="F210" s="20" t="s">
         <v>365</v>
       </c>
-      <c r="F210" s="20" t="s">
-        <v>366</v>
-      </c>
       <c r="G210" s="20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H210" s="55">
         <v>280376250</v>
@@ -22327,9 +22022,7 @@
         <f t="shared" si="31"/>
         <v>336115049</v>
       </c>
-      <c r="L210" s="34">
-        <v>45888</v>
-      </c>
+      <c r="L210" s="34"/>
       <c r="M210" s="40">
         <v>0</v>
       </c>
@@ -22391,7 +22084,7 @@
         <v>207</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C211" s="4">
         <v>45870</v>
@@ -22400,13 +22093,13 @@
         <v>2025</v>
       </c>
       <c r="E211" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F211" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="F211" s="13" t="s">
-        <v>366</v>
-      </c>
       <c r="G211" s="20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H211" s="55">
         <v>373835000</v>
@@ -22421,9 +22114,7 @@
         <f t="shared" si="31"/>
         <v>448153398</v>
       </c>
-      <c r="L211" s="34">
-        <v>45888</v>
-      </c>
+      <c r="L211" s="34"/>
       <c r="M211" s="40">
         <v>0</v>
       </c>
@@ -22485,7 +22176,7 @@
         <v>208</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C212" s="4">
         <v>45867</v>
@@ -22494,13 +22185,13 @@
         <v>2025</v>
       </c>
       <c r="E212" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="F212" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="G212" s="20" t="s">
         <v>399</v>
-      </c>
-      <c r="F212" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="G212" s="20" t="s">
-        <v>400</v>
       </c>
       <c r="H212" s="55">
         <v>13552600</v>
@@ -22515,9 +22206,7 @@
         <f t="shared" si="31"/>
         <v>15071846</v>
       </c>
-      <c r="L212" s="34">
-        <v>45869</v>
-      </c>
+      <c r="L212" s="34"/>
       <c r="M212" s="40">
         <v>0</v>
       </c>
@@ -22578,7 +22267,7 @@
         <v>209</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C213" s="4">
         <v>45877</v>
@@ -22593,7 +22282,7 @@
         <v>233</v>
       </c>
       <c r="G213" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H213" s="55">
         <v>23950123</v>
@@ -22608,9 +22297,7 @@
         <f t="shared" si="31"/>
         <v>24213574</v>
       </c>
-      <c r="L213" s="34">
-        <v>45911</v>
-      </c>
+      <c r="L213" s="34"/>
       <c r="M213" s="40">
         <v>0</v>
       </c>
@@ -22672,7 +22359,7 @@
         <v>210</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C214" s="4">
         <v>45877</v>
@@ -22687,7 +22374,7 @@
         <v>233</v>
       </c>
       <c r="G214" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H214" s="55">
         <v>23636289</v>
@@ -22702,9 +22389,7 @@
         <f t="shared" si="31"/>
         <v>23896288</v>
       </c>
-      <c r="L214" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L214" s="34"/>
       <c r="M214" s="40">
         <v>0</v>
       </c>
@@ -22759,7 +22444,7 @@
         <v>23423562</v>
       </c>
       <c r="AD214" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="215" spans="1:31" s="21" customFormat="1">
@@ -22768,7 +22453,7 @@
         <v>211</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C215" s="4">
         <v>45877</v>
@@ -22783,7 +22468,7 @@
         <v>233</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H215" s="55">
         <v>14686464</v>
@@ -22798,9 +22483,7 @@
         <f t="shared" si="31"/>
         <v>14848015</v>
       </c>
-      <c r="L215" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L215" s="34"/>
       <c r="M215" s="40">
         <v>0</v>
       </c>
@@ -22854,7 +22537,7 @@
         <v>14848015</v>
       </c>
       <c r="AD215" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="216" spans="1:31" s="21" customFormat="1">
@@ -22863,7 +22546,7 @@
         <v>212</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C216" s="4">
         <v>45877</v>
@@ -22878,7 +22561,7 @@
         <v>233</v>
       </c>
       <c r="G216" s="20" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H216" s="55">
         <v>48592500</v>
@@ -22893,9 +22576,7 @@
         <f t="shared" si="31"/>
         <v>49127018</v>
       </c>
-      <c r="L216" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L216" s="34"/>
       <c r="M216" s="40">
         <v>0</v>
       </c>
@@ -22950,7 +22631,7 @@
         <v>48155168</v>
       </c>
       <c r="AD216" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AE216" s="21" t="s">
         <v>1</v>
@@ -22962,7 +22643,7 @@
         <v>213</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C217" s="4">
         <v>45877</v>
@@ -22977,7 +22658,7 @@
         <v>233</v>
       </c>
       <c r="G217" s="20" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H217" s="55">
         <v>1045000</v>
@@ -22992,9 +22673,7 @@
         <f t="shared" si="31"/>
         <v>1056495</v>
       </c>
-      <c r="L217" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L217" s="34"/>
       <c r="M217" s="40">
         <v>0</v>
       </c>
@@ -23048,7 +22727,7 @@
         <v>1056495</v>
       </c>
       <c r="AD217" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AE217" s="76" t="s">
         <v>1</v>
@@ -23060,7 +22739,7 @@
         <v>214</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C218" s="4">
         <v>45877</v>
@@ -23075,7 +22754,7 @@
         <v>233</v>
       </c>
       <c r="G218" s="20" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H218" s="55">
         <v>91475934</v>
@@ -23090,9 +22769,7 @@
         <f t="shared" si="31"/>
         <v>92482169</v>
       </c>
-      <c r="L218" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L218" s="34"/>
       <c r="M218" s="40">
         <v>0</v>
       </c>
@@ -23147,7 +22824,7 @@
         <v>90652650</v>
       </c>
       <c r="AD218" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AE218" s="21" t="s">
         <v>1</v>
@@ -23159,7 +22836,7 @@
         <v>215</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C219" s="4">
         <v>45877</v>
@@ -23174,7 +22851,7 @@
         <v>233</v>
       </c>
       <c r="G219" s="20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H219" s="55">
         <v>18865000</v>
@@ -23189,9 +22866,7 @@
         <f t="shared" si="31"/>
         <v>19072515</v>
       </c>
-      <c r="L219" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L219" s="34"/>
       <c r="M219" s="40">
         <v>0</v>
       </c>
@@ -23246,7 +22921,7 @@
         <v>18695215</v>
       </c>
       <c r="AD219" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AE219" s="21" t="s">
         <v>1</v>
@@ -23258,7 +22933,7 @@
         <v>216</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C220" s="4">
         <v>45880</v>
@@ -23273,7 +22948,7 @@
         <v>233</v>
       </c>
       <c r="G220" s="20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H220" s="55">
         <v>25591853</v>
@@ -23288,9 +22963,7 @@
         <f t="shared" si="31"/>
         <v>25873363</v>
       </c>
-      <c r="L220" s="34">
-        <v>45894</v>
-      </c>
+      <c r="L220" s="34"/>
       <c r="M220" s="40">
         <v>0</v>
       </c>
@@ -23344,7 +23017,7 @@
         <v>25873363</v>
       </c>
       <c r="AD220" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AE220" s="21" t="s">
         <v>1</v>
@@ -23356,7 +23029,7 @@
         <v>217</v>
       </c>
       <c r="B221" s="26" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C221" s="79">
         <v>45880</v>
@@ -23371,7 +23044,7 @@
         <v>1</v>
       </c>
       <c r="G221" s="35" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H221" s="75">
         <v>0</v>
@@ -23386,9 +23059,7 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L221" s="71" t="s">
-        <v>1</v>
-      </c>
+      <c r="L221" s="71"/>
       <c r="M221" s="72">
         <v>0</v>
       </c>
@@ -23441,7 +23112,7 @@
         <v>0</v>
       </c>
       <c r="AD221" s="26" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="222" spans="1:31" s="31" customFormat="1">
@@ -23450,7 +23121,7 @@
         <v>218</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C222" s="4">
         <v>45884</v>
@@ -23465,7 +23136,7 @@
         <v>69</v>
       </c>
       <c r="G222" s="20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H222" s="55">
         <v>178200000</v>
@@ -23480,9 +23151,7 @@
         <f t="shared" si="31"/>
         <v>200178000</v>
       </c>
-      <c r="L222" s="34">
-        <v>45889</v>
-      </c>
+      <c r="L222" s="34"/>
       <c r="M222" s="40">
         <v>0</v>
       </c>
@@ -23537,7 +23206,7 @@
         <v>199782000</v>
       </c>
       <c r="AD222" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="223" spans="1:31" s="21" customFormat="1">
@@ -23546,7 +23215,7 @@
         <v>219</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C223" s="4">
         <v>45884</v>
@@ -23561,7 +23230,7 @@
         <v>69</v>
       </c>
       <c r="G223" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H223" s="55">
         <v>17691020</v>
@@ -23638,7 +23307,7 @@
         <v>220</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C224" s="4">
         <v>45884</v>
@@ -23653,7 +23322,7 @@
         <v>69</v>
       </c>
       <c r="G224" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H224" s="55">
         <v>132042312</v>
@@ -23668,9 +23337,7 @@
         <f t="shared" si="31"/>
         <v>148327530</v>
       </c>
-      <c r="L224" s="34">
-        <v>45889</v>
-      </c>
+      <c r="L224" s="34"/>
       <c r="M224" s="40">
         <v>0</v>
       </c>
@@ -23725,7 +23392,7 @@
         <v>148034103</v>
       </c>
       <c r="AD224" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="225" spans="1:30" s="31" customFormat="1">
@@ -23734,7 +23401,7 @@
         <v>221</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C225" s="4">
         <v>45884</v>
@@ -23749,7 +23416,7 @@
         <v>69</v>
       </c>
       <c r="G225" s="20" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H225" s="55">
         <v>133328606</v>
@@ -23764,9 +23431,7 @@
         <f t="shared" si="31"/>
         <v>149772467</v>
       </c>
-      <c r="L225" s="34">
-        <v>45889</v>
-      </c>
+      <c r="L225" s="34"/>
       <c r="M225" s="40">
         <v>0</v>
       </c>
@@ -23821,7 +23486,7 @@
         <v>149476181</v>
       </c>
       <c r="AD225" s="13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="226" spans="1:30" s="31" customFormat="1">
@@ -23830,7 +23495,7 @@
         <v>222</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C226" s="4">
         <v>45884</v>
@@ -23839,13 +23504,13 @@
         <v>2025</v>
       </c>
       <c r="E226" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="F226" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="F226" s="20" t="s">
+      <c r="G226" s="20" t="s">
         <v>437</v>
-      </c>
-      <c r="G226" s="20" t="s">
-        <v>438</v>
       </c>
       <c r="H226" s="55">
         <v>6000000</v>
@@ -23860,9 +23525,7 @@
         <f t="shared" si="31"/>
         <v>7326000</v>
       </c>
-      <c r="L226" s="34">
-        <v>45889</v>
-      </c>
+      <c r="L226" s="34"/>
       <c r="M226" s="40">
         <v>0</v>
       </c>
@@ -23923,7 +23586,7 @@
         <v>223</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C227" s="4">
         <v>45891</v>
@@ -23932,13 +23595,13 @@
         <v>2025</v>
       </c>
       <c r="E227" s="20" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F227" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="G227" s="20" t="s">
         <v>363</v>
-      </c>
-      <c r="G227" s="20" t="s">
-        <v>364</v>
       </c>
       <c r="H227" s="55">
         <v>68932417</v>
@@ -23953,9 +23616,7 @@
         <f t="shared" si="31"/>
         <v>76659741</v>
       </c>
-      <c r="L227" s="34">
-        <v>45953</v>
-      </c>
+      <c r="L227" s="34"/>
       <c r="M227" s="40">
         <v>0</v>
       </c>
@@ -24016,7 +23677,7 @@
         <v>224</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C228" s="4">
         <v>45891</v>
@@ -24025,13 +23686,13 @@
         <v>2025</v>
       </c>
       <c r="E228" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="F228" s="20" t="s">
         <v>362</v>
       </c>
-      <c r="F228" s="20" t="s">
+      <c r="G228" s="20" t="s">
         <v>363</v>
-      </c>
-      <c r="G228" s="20" t="s">
-        <v>364</v>
       </c>
       <c r="H228" s="55">
         <v>172857233</v>
@@ -24046,9 +23707,7 @@
         <f t="shared" si="31"/>
         <v>192234529</v>
       </c>
-      <c r="L228" s="34">
-        <v>45898</v>
-      </c>
+      <c r="L228" s="34"/>
       <c r="M228" s="40">
         <v>0</v>
       </c>
@@ -24110,7 +23769,7 @@
         <v>225</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C229" s="4">
         <v>45891</v>
@@ -24119,13 +23778,13 @@
         <v>2025</v>
       </c>
       <c r="E229" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="F229" s="20" t="s">
         <v>362</v>
       </c>
-      <c r="F229" s="20" t="s">
-        <v>363</v>
-      </c>
       <c r="G229" s="20" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H229" s="55">
         <v>18562550</v>
@@ -24140,9 +23799,7 @@
         <f t="shared" si="31"/>
         <v>20643412</v>
       </c>
-      <c r="L229" s="34">
-        <v>45940</v>
-      </c>
+      <c r="L229" s="34"/>
       <c r="M229" s="40">
         <v>0</v>
       </c>
@@ -24204,7 +23861,7 @@
         <v>226</v>
       </c>
       <c r="B230" s="26" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C230" s="79">
         <v>45891</v>
@@ -24219,7 +23876,7 @@
         <v>1</v>
       </c>
       <c r="G230" s="35" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H230" s="75">
         <v>0</v>
@@ -24296,7 +23953,7 @@
         <v>227</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C231" s="4">
         <v>45891</v>
@@ -24305,13 +23962,13 @@
         <v>2025</v>
       </c>
       <c r="E231" s="20" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F231" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="G231" s="20" t="s">
         <v>371</v>
-      </c>
-      <c r="G231" s="20" t="s">
-        <v>372</v>
       </c>
       <c r="H231" s="55">
         <v>31250000</v>
@@ -24326,9 +23983,7 @@
         <f t="shared" si="31"/>
         <v>38156250</v>
       </c>
-      <c r="L231" s="34">
-        <v>45938</v>
-      </c>
+      <c r="L231" s="34"/>
       <c r="M231" s="40">
         <v>0</v>
       </c>
@@ -24390,7 +24045,7 @@
         <v>228</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C232" s="4">
         <v>45896</v>
@@ -24399,13 +24054,13 @@
         <v>2025</v>
       </c>
       <c r="E232" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="F232" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="G232" s="20" t="s">
         <v>450</v>
-      </c>
-      <c r="F232" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="G232" s="20" t="s">
-        <v>451</v>
       </c>
       <c r="H232" s="55">
         <v>638626500</v>
@@ -24420,9 +24075,7 @@
         <f t="shared" si="31"/>
         <v>697303503</v>
       </c>
-      <c r="L232" s="34">
-        <v>45916</v>
-      </c>
+      <c r="L232" s="34"/>
       <c r="M232" s="40">
         <v>0</v>
       </c>
@@ -24484,7 +24137,7 @@
         <v>229</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C233" s="4">
         <v>45986</v>
@@ -24493,13 +24146,13 @@
         <v>2025</v>
       </c>
       <c r="E233" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="F233" s="20" t="s">
         <v>365</v>
       </c>
-      <c r="F233" s="20" t="s">
-        <v>366</v>
-      </c>
       <c r="G233" s="20" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H233" s="55">
         <v>323027750</v>
@@ -24514,9 +24167,7 @@
         <f t="shared" si="31"/>
         <v>387245667</v>
       </c>
-      <c r="L233" s="34">
-        <v>45996</v>
-      </c>
+      <c r="L233" s="34"/>
       <c r="M233" s="40">
         <v>0</v>
       </c>
@@ -24578,7 +24229,7 @@
         <v>230</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C234" s="4">
         <v>45904</v>
@@ -24587,13 +24238,13 @@
         <v>2025</v>
       </c>
       <c r="E234" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F234" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G234" s="20" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H234" s="55">
         <v>4041667</v>
@@ -24608,9 +24259,7 @@
         <f t="shared" si="31"/>
         <v>4486250</v>
       </c>
-      <c r="L234" s="34">
-        <v>45931</v>
-      </c>
+      <c r="L234" s="34"/>
       <c r="M234" s="40">
         <v>0</v>
       </c>
@@ -24671,7 +24320,7 @@
         <v>231</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C235" s="4">
         <v>45904</v>
@@ -24680,13 +24329,13 @@
         <v>2025</v>
       </c>
       <c r="E235" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F235" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G235" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H235" s="55">
         <v>4041667</v>
@@ -24701,9 +24350,7 @@
         <f t="shared" si="31"/>
         <v>4486250</v>
       </c>
-      <c r="L235" s="34">
-        <v>45939</v>
-      </c>
+      <c r="L235" s="34"/>
       <c r="M235" s="40">
         <v>0</v>
       </c>
@@ -24764,7 +24411,7 @@
         <v>232</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C236" s="4">
         <v>45904</v>
@@ -24773,13 +24420,13 @@
         <v>2025</v>
       </c>
       <c r="E236" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F236" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G236" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H236" s="55">
         <v>4041667</v>
@@ -24794,9 +24441,7 @@
         <f t="shared" si="31"/>
         <v>4486250</v>
       </c>
-      <c r="L236" s="34">
-        <v>45945</v>
-      </c>
+      <c r="L236" s="34"/>
       <c r="M236" s="40">
         <v>0</v>
       </c>
@@ -24857,7 +24502,7 @@
         <v>233</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C237" s="4">
         <v>45904</v>
@@ -24866,13 +24511,13 @@
         <v>2025</v>
       </c>
       <c r="E237" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F237" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G237" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H237" s="55">
         <v>4041667</v>
@@ -24887,9 +24532,7 @@
         <f t="shared" si="31"/>
         <v>4486250</v>
       </c>
-      <c r="L237" s="34">
-        <v>45959</v>
-      </c>
+      <c r="L237" s="34"/>
       <c r="M237" s="40">
         <v>0</v>
       </c>
@@ -24950,7 +24593,7 @@
         <v>234</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C238" s="4">
         <v>45904</v>
@@ -24959,13 +24602,13 @@
         <v>2025</v>
       </c>
       <c r="E238" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F238" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G238" s="20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H238" s="55">
         <v>5388889</v>
@@ -24980,9 +24623,7 @@
         <f t="shared" si="31"/>
         <v>5981667</v>
       </c>
-      <c r="L238" s="34">
-        <v>45946</v>
-      </c>
+      <c r="L238" s="34"/>
       <c r="M238" s="40">
         <v>0</v>
       </c>
@@ -25043,7 +24684,7 @@
         <v>235</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C239" s="4">
         <v>45904</v>
@@ -25052,13 +24693,13 @@
         <v>2025</v>
       </c>
       <c r="E239" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F239" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G239" s="20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H239" s="55">
         <v>5388889</v>
@@ -25135,7 +24776,7 @@
         <v>236</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C240" s="4">
         <v>45904</v>
@@ -25144,13 +24785,13 @@
         <v>2025</v>
       </c>
       <c r="E240" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F240" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G240" s="20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H240" s="55">
         <v>5388889</v>
@@ -25226,7 +24867,7 @@
         <v>237</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C241" s="4">
         <v>45904</v>
@@ -25235,13 +24876,13 @@
         <v>2025</v>
       </c>
       <c r="E241" s="13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F241" s="13" t="s">
         <v>73</v>
       </c>
       <c r="G241" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H241" s="55">
         <v>16166665</v>
@@ -25256,9 +24897,7 @@
         <f t="shared" si="31"/>
         <v>17944998</v>
       </c>
-      <c r="L241" s="34">
-        <v>45943</v>
-      </c>
+      <c r="L241" s="34"/>
       <c r="M241" s="40">
         <v>0</v>
       </c>
@@ -25319,7 +24958,7 @@
         <v>238</v>
       </c>
       <c r="B242" s="26" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C242" s="79">
         <v>45918</v>
@@ -25334,7 +24973,7 @@
         <v>1</v>
       </c>
       <c r="G242" s="35" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H242" s="75">
         <v>0</v>
@@ -25404,7 +25043,7 @@
         <v>0</v>
       </c>
       <c r="AD242" s="26" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="243" spans="1:30" s="21" customFormat="1">
@@ -25413,7 +25052,7 @@
         <v>239</v>
       </c>
       <c r="B243" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C243" s="79">
         <v>45922</v>
@@ -25428,7 +25067,7 @@
         <v>1</v>
       </c>
       <c r="G243" s="35" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H243" s="75">
         <v>0</v>
@@ -25505,7 +25144,7 @@
         <v>240</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C244" s="4">
         <v>45929</v>
@@ -25514,13 +25153,13 @@
         <v>2025</v>
       </c>
       <c r="E244" s="20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F244" s="20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G244" s="20" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H244" s="55">
         <v>709185000</v>
@@ -25535,9 +25174,7 @@
         <f t="shared" si="31"/>
         <v>842299025</v>
       </c>
-      <c r="L244" s="34">
-        <v>45960</v>
-      </c>
+      <c r="L244" s="34"/>
       <c r="M244" s="40">
         <v>0</v>
       </c>
@@ -25599,7 +25236,7 @@
         <v>241</v>
       </c>
       <c r="B245" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C245" s="79">
         <v>45943</v>
@@ -25614,7 +25251,7 @@
         <v>1</v>
       </c>
       <c r="G245" s="35" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H245" s="75">
         <v>0</v>
@@ -25691,7 +25328,7 @@
         <v>242</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C246" s="4">
         <v>45944</v>
@@ -25700,13 +25337,13 @@
         <v>2025</v>
       </c>
       <c r="E246" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F246" s="20" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G246" s="20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H246" s="55">
         <v>1592675000</v>
@@ -25721,9 +25358,7 @@
         <f t="shared" si="31"/>
         <v>1909298790</v>
       </c>
-      <c r="L246" s="34">
-        <v>45951</v>
-      </c>
+      <c r="L246" s="34"/>
       <c r="M246" s="40">
         <v>0</v>
       </c>
@@ -25779,7 +25414,7 @@
         <v>1906750510</v>
       </c>
       <c r="AD246" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="247" spans="1:30" s="31" customFormat="1">
@@ -25788,7 +25423,7 @@
         <v>243</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C247" s="4">
         <v>45999</v>
@@ -25797,13 +25432,13 @@
         <v>2025</v>
       </c>
       <c r="E247" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="F247" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="G247" s="20" t="s">
         <v>596</v>
-      </c>
-      <c r="F247" s="20" t="s">
-        <v>525</v>
-      </c>
-      <c r="G247" s="20" t="s">
-        <v>597</v>
       </c>
       <c r="H247" s="55">
         <v>326442500</v>
@@ -25882,7 +25517,7 @@
         <v>244</v>
       </c>
       <c r="B248" s="26" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C248" s="79">
         <v>45768</v>
@@ -25897,7 +25532,7 @@
         <v>1</v>
       </c>
       <c r="G248" s="35" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H248" s="75">
         <v>0</v>
@@ -25974,7 +25609,7 @@
         <v>245</v>
       </c>
       <c r="B249" s="26" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C249" s="79">
         <v>45729</v>
@@ -25989,7 +25624,7 @@
         <v>1</v>
       </c>
       <c r="G249" s="35" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H249" s="75">
         <v>0</v>
@@ -26066,7 +25701,7 @@
         <v>246</v>
       </c>
       <c r="B250" s="26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C250" s="79">
         <v>45756</v>
@@ -26081,7 +25716,7 @@
         <v>1</v>
       </c>
       <c r="G250" s="35" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H250" s="74">
         <v>0</v>
@@ -26158,7 +25793,7 @@
         <v>247</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C251" s="4">
         <v>46009</v>
@@ -26167,13 +25802,13 @@
         <v>2025</v>
       </c>
       <c r="E251" s="20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F251" s="20" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G251" s="20" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H251" s="55">
         <v>93218500</v>
@@ -26250,7 +25885,7 @@
         <v>248</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C252" s="4">
         <v>46009</v>
@@ -26259,13 +25894,13 @@
         <v>2025</v>
       </c>
       <c r="E252" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="F252" s="20" t="s">
+        <v>632</v>
+      </c>
+      <c r="G252" s="20" t="s">
         <v>622</v>
-      </c>
-      <c r="F252" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="G252" s="20" t="s">
-        <v>623</v>
       </c>
       <c r="H252" s="55">
         <v>44812500</v>
@@ -26342,7 +25977,7 @@
         <v>249</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C253" s="4">
         <v>46020</v>
@@ -26351,13 +25986,13 @@
         <v>2025</v>
       </c>
       <c r="E253" s="20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F253" s="20" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G253" s="20" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H253" s="55">
         <v>4500000</v>
@@ -26434,7 +26069,7 @@
         <v>250</v>
       </c>
       <c r="B254" s="26" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C254" s="79">
         <v>46002</v>
@@ -26449,7 +26084,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="76" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H254" s="75">
         <v>0</v>
@@ -26526,7 +26161,7 @@
         <v>251</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C255" s="4">
         <v>46002</v>
@@ -26535,13 +26170,13 @@
         <v>2025</v>
       </c>
       <c r="E255" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F255" s="20" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G255" s="21" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H255" s="55">
         <v>166400000</v>
@@ -26618,7 +26253,7 @@
         <v>252</v>
       </c>
       <c r="B256" s="26" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C256" s="79">
         <v>45979</v>
@@ -26633,7 +26268,7 @@
         <v>1</v>
       </c>
       <c r="G256" s="76" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H256" s="75">
         <v>0</v>
@@ -26692,11 +26327,11 @@
         <v>0</v>
       </c>
       <c r="AA256" s="62">
-        <f t="shared" ref="AA256:AA303" si="38">-(H256+I256)*2%</f>
+        <f t="shared" ref="AA256:AA302" si="38">-(H256+I256)*2%</f>
         <v>0</v>
       </c>
       <c r="AB256" s="62">
-        <f t="shared" ref="AB256:AB303" si="39">K256+Z256+AA256</f>
+        <f t="shared" ref="AB256:AB302" si="39">K256+Z256+AA256</f>
         <v>0</v>
       </c>
       <c r="AC256" s="75">
@@ -26710,7 +26345,7 @@
         <v>253</v>
       </c>
       <c r="B257" s="26" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C257" s="79">
         <v>45980</v>
@@ -26725,7 +26360,7 @@
         <v>1</v>
       </c>
       <c r="G257" s="76" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H257" s="75">
         <v>0</v>
@@ -26802,7 +26437,7 @@
         <v>254</v>
       </c>
       <c r="B258" s="26" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C258" s="79">
         <v>45999</v>
@@ -26817,7 +26452,7 @@
         <v>1</v>
       </c>
       <c r="G258" s="76" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H258" s="75">
         <v>0</v>
@@ -26894,7 +26529,7 @@
         <v>255</v>
       </c>
       <c r="B259" s="26" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C259" s="79">
         <v>45999</v>
@@ -26909,7 +26544,7 @@
         <v>1</v>
       </c>
       <c r="G259" s="76" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H259" s="75">
         <v>0</v>
@@ -26986,7 +26621,7 @@
         <v>256</v>
       </c>
       <c r="B260" s="26" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C260" s="79">
         <v>45982</v>
@@ -27001,7 +26636,7 @@
         <v>1</v>
       </c>
       <c r="G260" s="76" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H260" s="75">
         <v>0</v>
@@ -27078,7 +26713,7 @@
         <v>257</v>
       </c>
       <c r="B261" s="26" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C261" s="79">
         <v>45982</v>
@@ -27093,7 +26728,7 @@
         <v>1</v>
       </c>
       <c r="G261" s="76" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H261" s="75">
         <v>0</v>
@@ -27105,7 +26740,7 @@
         <v>0</v>
       </c>
       <c r="K261" s="72">
-        <f t="shared" ref="K261:K303" si="40">SUM(H261:J261)</f>
+        <f t="shared" ref="K261:K302" si="40">SUM(H261:J261)</f>
         <v>0</v>
       </c>
       <c r="L261" s="71"/>
@@ -27143,12 +26778,12 @@
         <v>0</v>
       </c>
       <c r="X261" s="62">
-        <f t="shared" ref="X261:X303" si="41">K261-SUM(M261:W261)</f>
+        <f t="shared" ref="X261:X302" si="41">K261-SUM(M261:W261)</f>
         <v>0</v>
       </c>
       <c r="Y261" s="62"/>
       <c r="Z261" s="73">
-        <f t="shared" ref="Z261:Z303" si="42">-J261</f>
+        <f t="shared" ref="Z261:Z302" si="42">-J261</f>
         <v>0</v>
       </c>
       <c r="AA261" s="62">
@@ -27170,7 +26805,7 @@
         <v>258</v>
       </c>
       <c r="B262" s="26" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C262" s="79">
         <v>45983</v>
@@ -27185,7 +26820,7 @@
         <v>25</v>
       </c>
       <c r="G262" s="76" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H262" s="75">
         <v>0</v>
@@ -27262,7 +26897,7 @@
         <v>259</v>
       </c>
       <c r="B263" s="26" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C263" s="79">
         <v>45983</v>
@@ -27277,7 +26912,7 @@
         <v>1</v>
       </c>
       <c r="G263" s="76" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H263" s="75">
         <v>0</v>
@@ -28250,7 +27885,7 @@
         <v>1</v>
       </c>
       <c r="F274" s="22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G274" s="22" t="s">
         <v>1</v>
@@ -28324,95 +27959,97 @@
       </c>
       <c r="AD274" s="7"/>
     </row>
-    <row r="275" spans="1:30" s="31" customFormat="1">
-      <c r="A275" s="28">
+    <row r="275" spans="1:30" s="21" customFormat="1">
+      <c r="A275" s="19">
         <f t="shared" si="43"/>
         <v>271</v>
       </c>
-      <c r="B275" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C275" s="80"/>
-      <c r="D275" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="E275" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F275" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G275" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="H275" s="58">
-        <v>0</v>
-      </c>
-      <c r="I275" s="58">
-        <v>0</v>
-      </c>
-      <c r="J275" s="58">
-        <v>0</v>
-      </c>
-      <c r="K275" s="41">
+      <c r="B275" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C275" s="4"/>
+      <c r="D275" s="2">
+        <v>2025</v>
+      </c>
+      <c r="E275" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F275" s="20" t="s">
+        <v>518</v>
+      </c>
+      <c r="G275" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="H275" s="55">
+        <v>250000000</v>
+      </c>
+      <c r="I275" s="55">
+        <v>0</v>
+      </c>
+      <c r="J275" s="55">
+        <v>0</v>
+      </c>
+      <c r="K275" s="40">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="L275" s="68"/>
-      <c r="M275" s="41">
-        <v>0</v>
-      </c>
-      <c r="N275" s="42">
-        <v>0</v>
-      </c>
-      <c r="O275" s="42">
-        <v>0</v>
-      </c>
-      <c r="P275" s="42">
-        <v>0</v>
-      </c>
-      <c r="Q275" s="42">
-        <v>0</v>
-      </c>
-      <c r="R275" s="42">
-        <v>0</v>
-      </c>
-      <c r="S275" s="42">
-        <v>0</v>
-      </c>
-      <c r="T275" s="42">
-        <v>0</v>
-      </c>
-      <c r="U275" s="42">
-        <v>0</v>
-      </c>
-      <c r="V275" s="42">
-        <v>0</v>
-      </c>
-      <c r="W275" s="42">
-        <v>0</v>
-      </c>
-      <c r="X275" s="42">
+        <v>250000000</v>
+      </c>
+      <c r="L275" s="34"/>
+      <c r="M275" s="40">
+        <v>0</v>
+      </c>
+      <c r="N275" s="39">
+        <v>0</v>
+      </c>
+      <c r="O275" s="39">
+        <v>0</v>
+      </c>
+      <c r="P275" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q275" s="39">
+        <v>0</v>
+      </c>
+      <c r="R275" s="39">
+        <v>0</v>
+      </c>
+      <c r="S275" s="39">
+        <v>0</v>
+      </c>
+      <c r="T275" s="39">
+        <v>0</v>
+      </c>
+      <c r="U275" s="39">
+        <v>0</v>
+      </c>
+      <c r="V275" s="39">
+        <v>0</v>
+      </c>
+      <c r="W275" s="39">
+        <v>0</v>
+      </c>
+      <c r="X275" s="39">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="Y275" s="42"/>
-      <c r="Z275" s="56">
+        <v>250000000</v>
+      </c>
+      <c r="Y275" s="39"/>
+      <c r="Z275" s="23">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AA275" s="42">
+      <c r="AA275" s="39">
         <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="AB275" s="42">
+        <v>-5000000</v>
+      </c>
+      <c r="AB275" s="39">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="AC275" s="58">
-        <v>0</v>
-      </c>
-      <c r="AD275" s="7"/>
+        <v>245000000</v>
+      </c>
+      <c r="AC275" s="55">
+        <v>0</v>
+      </c>
+      <c r="AD275" s="96" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="276" spans="1:30" s="21" customFormat="1">
       <c r="A276" s="28">
@@ -28430,7 +28067,7 @@
         <v>1</v>
       </c>
       <c r="F276" s="22" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G276" s="22" t="s">
         <v>1</v>
@@ -28700,7 +28337,7 @@
         <v>1</v>
       </c>
       <c r="F279" s="22" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G279" s="22" t="s">
         <v>1</v>
@@ -28790,7 +28427,7 @@
         <v>1</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G280" s="22" t="s">
         <v>1</v>
@@ -28968,7 +28605,7 @@
         <v>1</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G282" s="22" t="s">
         <v>1</v>
@@ -29148,7 +28785,7 @@
         <v>1</v>
       </c>
       <c r="F284" s="22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G284" s="22" t="s">
         <v>1</v>
@@ -29238,7 +28875,7 @@
         <v>1</v>
       </c>
       <c r="F285" s="22" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G285" s="22" t="s">
         <v>1</v>
@@ -29328,7 +28965,7 @@
         <v>1</v>
       </c>
       <c r="F286" s="22" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G286" s="22" t="s">
         <v>1</v>
@@ -29418,7 +29055,7 @@
         <v>1</v>
       </c>
       <c r="F287" s="22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G287" s="22" t="s">
         <v>1</v>
@@ -30802,384 +30439,295 @@
       </c>
       <c r="AD302" s="7"/>
     </row>
-    <row r="303" spans="1:30" s="21" customFormat="1">
-      <c r="A303" s="19"/>
-      <c r="B303" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="C303" s="79">
-        <v>46097</v>
-      </c>
-      <c r="D303" s="25">
-        <v>2026</v>
-      </c>
-      <c r="E303" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="F303" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="G303" s="31" t="s">
-        <v>650</v>
-      </c>
-      <c r="H303" s="55">
-        <v>196018396</v>
-      </c>
-      <c r="I303" s="55">
-        <v>3339160</v>
-      </c>
-      <c r="J303" s="55">
-        <v>21929331</v>
-      </c>
-      <c r="K303" s="40">
-        <f t="shared" si="40"/>
-        <v>221286887</v>
-      </c>
-      <c r="L303" s="55"/>
-      <c r="M303" s="55">
-        <v>0</v>
-      </c>
-      <c r="N303" s="55">
-        <v>0</v>
-      </c>
-      <c r="O303" s="55">
-        <v>0</v>
-      </c>
-      <c r="P303" s="55">
-        <v>0</v>
-      </c>
-      <c r="Q303" s="55">
-        <v>0</v>
-      </c>
-      <c r="R303" s="55">
-        <v>0</v>
-      </c>
-      <c r="S303" s="55">
-        <v>0</v>
-      </c>
-      <c r="T303" s="55">
-        <v>0</v>
-      </c>
-      <c r="U303" s="55">
-        <v>0</v>
-      </c>
-      <c r="V303" s="55">
-        <v>0</v>
-      </c>
-      <c r="W303" s="55">
-        <v>0</v>
-      </c>
-      <c r="X303" s="39">
-        <f t="shared" si="41"/>
-        <v>221286887</v>
-      </c>
-      <c r="Y303" s="42"/>
-      <c r="Z303" s="8">
-        <f t="shared" si="42"/>
-        <v>-21929331</v>
-      </c>
-      <c r="AA303" s="42">
-        <f t="shared" si="38"/>
-        <v>-3987151.12</v>
-      </c>
-      <c r="AB303" s="42">
-        <f t="shared" si="39"/>
-        <v>195370404.88</v>
-      </c>
-      <c r="AC303" s="55">
-        <v>0</v>
-      </c>
-      <c r="AD303" s="7"/>
-    </row>
-    <row r="305" spans="1:29">
-      <c r="H305" s="95">
-        <f>SUBTOTAL(9,H5:H304)</f>
-        <v>36846798127</v>
-      </c>
-      <c r="I305" s="95">
-        <f>SUBTOTAL(9,I5:I304)</f>
+    <row r="304" spans="1:30">
+      <c r="H304" s="95">
+        <f>SUBTOTAL(9,H5:H303)</f>
+        <v>37096798127</v>
+      </c>
+      <c r="I304" s="95">
+        <f>SUBTOTAL(9,I5:I303)</f>
         <v>1968234610</v>
       </c>
-      <c r="J305" s="95">
-        <f>SUBTOTAL(9,J5:J304)</f>
+      <c r="J304" s="95">
+        <f>SUBTOTAL(9,J5:J303)</f>
         <v>3409059096</v>
       </c>
-      <c r="K305" s="95">
-        <f>SUBTOTAL(9,K5:K304)</f>
-        <v>42224091833</v>
-      </c>
-      <c r="M305" s="32">
-        <f t="shared" ref="M305:X305" si="44">SUBTOTAL(9,M5:M304)</f>
+      <c r="K304" s="95">
+        <f>SUBTOTAL(9,K5:K303)</f>
+        <v>42474091833</v>
+      </c>
+      <c r="M304" s="32">
+        <f t="shared" ref="M304:X304" si="44">SUBTOTAL(9,M5:M303)</f>
         <v>3219609931</v>
       </c>
-      <c r="N305" s="32">
+      <c r="N304" s="32">
         <f t="shared" si="44"/>
         <v>4487221366</v>
       </c>
-      <c r="O305" s="32">
+      <c r="O304" s="32">
         <f t="shared" si="44"/>
         <v>16837158203.34</v>
       </c>
-      <c r="P305" s="32">
+      <c r="P304" s="32">
         <f t="shared" si="44"/>
         <v>3819509838.0999999</v>
       </c>
-      <c r="Q305" s="86">
+      <c r="Q304" s="86">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="R305" s="32">
+      <c r="R304" s="32">
         <f t="shared" si="44"/>
         <v>3915394741</v>
       </c>
-      <c r="S305" s="32">
+      <c r="S304" s="32">
         <f t="shared" si="44"/>
         <v>2978073566</v>
       </c>
-      <c r="T305" s="86">
+      <c r="T304" s="86">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="U305" s="32">
+      <c r="U304" s="32">
         <f t="shared" si="44"/>
         <v>1151031287</v>
       </c>
-      <c r="V305" s="86">
+      <c r="V304" s="86">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="W305" s="32">
+      <c r="W304" s="32">
         <f t="shared" si="44"/>
         <v>3154953380.5599999</v>
       </c>
-      <c r="X305" s="32">
+      <c r="X304" s="32">
         <f t="shared" si="44"/>
-        <v>2661139520</v>
-      </c>
-      <c r="Z305" s="32">
-        <f>SUBTOTAL(9,Z5:Z304)</f>
+        <v>2911139520</v>
+      </c>
+      <c r="Z304" s="32">
+        <f>SUBTOTAL(9,Z5:Z303)</f>
         <v>-3409059096</v>
       </c>
-      <c r="AA305" s="32">
-        <f>SUBTOTAL(9,AA5:AA304)</f>
-        <v>-561106685.36000001</v>
-      </c>
-      <c r="AB305" s="32">
-        <f>SUBTOTAL(9,AB5:AB304)</f>
-        <v>25042353648.540001</v>
-      </c>
-      <c r="AC305" s="32">
-        <f>SUBTOTAL(9,AC5:AC304)</f>
+      <c r="AA304" s="32">
+        <f>SUBTOTAL(9,AA5:AA303)</f>
+        <v>-562119534.24000001</v>
+      </c>
+      <c r="AB304" s="32">
+        <f>SUBTOTAL(9,AB5:AB303)</f>
+        <v>25091983243.66</v>
+      </c>
+      <c r="AC304" s="32">
+        <f>SUBTOTAL(9,AC5:AC303)</f>
         <v>10727544248.1</v>
       </c>
     </row>
-    <row r="306" spans="1:29">
-      <c r="H306" s="95"/>
-      <c r="I306" s="95"/>
-      <c r="J306" s="95"/>
-      <c r="K306" s="95"/>
-      <c r="M306" s="32"/>
-      <c r="N306" s="32"/>
-      <c r="O306" s="32"/>
-      <c r="P306" s="32"/>
-      <c r="Q306" s="32"/>
-      <c r="R306" s="32"/>
-      <c r="S306" s="32"/>
-      <c r="T306" s="32"/>
-      <c r="U306" s="32"/>
-      <c r="V306" s="32"/>
-      <c r="W306" s="32"/>
-      <c r="X306" s="32"/>
-      <c r="Z306" s="32"/>
-      <c r="AA306" s="32"/>
-      <c r="AB306" s="32"/>
-      <c r="AC306" s="32"/>
-    </row>
-    <row r="307" spans="1:29" s="35" customFormat="1">
-      <c r="A307" s="64"/>
-      <c r="C307" s="70"/>
-      <c r="D307" s="64"/>
-      <c r="H307" s="72"/>
-      <c r="I307" s="72"/>
-      <c r="J307" s="72"/>
-      <c r="K307" s="72"/>
-      <c r="L307" s="70"/>
-      <c r="M307" s="65">
+    <row r="305" spans="1:29">
+      <c r="H305" s="95"/>
+      <c r="I305" s="95"/>
+      <c r="J305" s="95"/>
+      <c r="K305" s="95"/>
+      <c r="M305" s="32"/>
+      <c r="N305" s="32"/>
+      <c r="O305" s="32"/>
+      <c r="P305" s="32"/>
+      <c r="Q305" s="32"/>
+      <c r="R305" s="32"/>
+      <c r="S305" s="32"/>
+      <c r="T305" s="32"/>
+      <c r="U305" s="32"/>
+      <c r="V305" s="32"/>
+      <c r="W305" s="32"/>
+      <c r="X305" s="32"/>
+      <c r="Z305" s="32"/>
+      <c r="AA305" s="32"/>
+      <c r="AB305" s="32"/>
+      <c r="AC305" s="32"/>
+    </row>
+    <row r="306" spans="1:29" s="35" customFormat="1">
+      <c r="A306" s="64"/>
+      <c r="C306" s="70"/>
+      <c r="D306" s="64"/>
+      <c r="H306" s="72"/>
+      <c r="I306" s="72"/>
+      <c r="J306" s="72"/>
+      <c r="K306" s="72"/>
+      <c r="L306" s="70"/>
+      <c r="M306" s="65">
         <v>3219609931</v>
       </c>
-      <c r="N307" s="65">
+      <c r="N306" s="65">
         <v>4487221366</v>
       </c>
-      <c r="O307" s="65">
+      <c r="O306" s="65">
         <v>16837158203.34</v>
       </c>
-      <c r="P307" s="65">
+      <c r="P306" s="65">
         <v>3819509838.0999999</v>
       </c>
-      <c r="Q307" s="65"/>
-      <c r="R307" s="65">
+      <c r="Q306" s="65"/>
+      <c r="R306" s="65">
         <v>3915394741</v>
       </c>
-      <c r="S307" s="65">
+      <c r="S306" s="65">
         <v>2978073566</v>
       </c>
-      <c r="T307" s="65"/>
-      <c r="U307" s="65">
+      <c r="T306" s="65"/>
+      <c r="U306" s="65">
         <v>1151031287</v>
       </c>
-      <c r="V307" s="65"/>
-      <c r="W307" s="65">
+      <c r="V306" s="65"/>
+      <c r="W306" s="65">
         <v>3154953380.5599999</v>
       </c>
-      <c r="X307" s="65"/>
-      <c r="Y307" s="66"/>
-      <c r="Z307" s="65"/>
-      <c r="AA307" s="65"/>
-      <c r="AB307" s="65"/>
-      <c r="AC307" s="65"/>
-    </row>
-    <row r="308" spans="1:29">
-      <c r="H308" s="95"/>
-      <c r="I308" s="95"/>
-      <c r="J308" s="95"/>
-      <c r="K308" s="95"/>
-      <c r="M308" s="32"/>
-      <c r="N308" s="32"/>
-      <c r="O308" s="32"/>
-      <c r="P308" s="32"/>
-      <c r="Q308" s="32"/>
-      <c r="R308" s="32"/>
-      <c r="S308" s="32"/>
-      <c r="T308" s="32"/>
-      <c r="U308" s="32"/>
-      <c r="V308" s="32"/>
-      <c r="W308" s="32"/>
-      <c r="X308" s="32"/>
-      <c r="Z308" s="32"/>
-      <c r="AA308" s="32"/>
-      <c r="AB308" s="32"/>
-      <c r="AC308" s="32"/>
-    </row>
-    <row r="309" spans="1:29" s="22" customFormat="1">
-      <c r="A309" s="28"/>
-      <c r="C309" s="69"/>
-      <c r="D309" s="28"/>
-      <c r="H309" s="41"/>
-      <c r="I309" s="41"/>
-      <c r="J309" s="41"/>
-      <c r="K309" s="41"/>
-      <c r="L309" s="69"/>
-      <c r="M309" s="29">
-        <f>M305-M307</f>
-        <v>0</v>
-      </c>
-      <c r="N309" s="29">
-        <f>N305-N307</f>
-        <v>0</v>
-      </c>
-      <c r="O309" s="29">
-        <f>O305-O307</f>
-        <v>0</v>
-      </c>
-      <c r="P309" s="29">
-        <f>P305-P307</f>
-        <v>0</v>
-      </c>
-      <c r="Q309" s="29"/>
-      <c r="R309" s="29">
-        <f>R305-R307</f>
-        <v>0</v>
-      </c>
-      <c r="S309" s="29">
-        <f>S305-S307</f>
-        <v>0</v>
-      </c>
-      <c r="T309" s="29">
-        <f>T305-T307</f>
-        <v>0</v>
-      </c>
-      <c r="U309" s="29">
-        <f>U305-U307</f>
-        <v>0</v>
-      </c>
-      <c r="V309" s="29"/>
-      <c r="W309" s="29">
-        <f>W305-W307</f>
-        <v>0</v>
-      </c>
-      <c r="X309" s="29"/>
-      <c r="Y309" s="56"/>
-      <c r="Z309" s="29"/>
-      <c r="AA309" s="29"/>
-      <c r="AB309" s="29"/>
-      <c r="AC309" s="29"/>
-    </row>
-    <row r="310" spans="1:29">
-      <c r="H310" s="95"/>
-      <c r="I310" s="95"/>
-      <c r="J310" s="95"/>
-      <c r="K310" s="95"/>
-      <c r="M310" s="32"/>
-      <c r="N310" s="32"/>
-      <c r="O310" s="32"/>
-      <c r="P310" s="32"/>
-      <c r="Q310" s="32"/>
-      <c r="R310" s="32"/>
-      <c r="S310" s="32"/>
-      <c r="T310" s="32"/>
-      <c r="U310" s="32"/>
-      <c r="V310" s="32"/>
-      <c r="W310" s="32"/>
-      <c r="X310" s="32"/>
-      <c r="Z310" s="32"/>
-      <c r="AA310" s="32"/>
-      <c r="AB310" s="32"/>
-      <c r="AC310" s="32"/>
-    </row>
-    <row r="311" spans="1:29" s="22" customFormat="1">
-      <c r="A311" s="28"/>
-      <c r="B311" s="7" t="s">
+      <c r="X306" s="65"/>
+      <c r="Y306" s="66"/>
+      <c r="Z306" s="65"/>
+      <c r="AA306" s="65"/>
+      <c r="AB306" s="65"/>
+      <c r="AC306" s="65"/>
+    </row>
+    <row r="307" spans="1:29">
+      <c r="H307" s="95"/>
+      <c r="I307" s="95"/>
+      <c r="J307" s="95"/>
+      <c r="K307" s="95"/>
+      <c r="M307" s="32"/>
+      <c r="N307" s="32"/>
+      <c r="O307" s="32"/>
+      <c r="P307" s="32"/>
+      <c r="Q307" s="32"/>
+      <c r="R307" s="32"/>
+      <c r="S307" s="32"/>
+      <c r="T307" s="32"/>
+      <c r="U307" s="32"/>
+      <c r="V307" s="32"/>
+      <c r="W307" s="32"/>
+      <c r="X307" s="32"/>
+      <c r="Z307" s="32"/>
+      <c r="AA307" s="32"/>
+      <c r="AB307" s="32"/>
+      <c r="AC307" s="32"/>
+    </row>
+    <row r="308" spans="1:29" s="22" customFormat="1">
+      <c r="A308" s="28"/>
+      <c r="C308" s="69"/>
+      <c r="D308" s="28"/>
+      <c r="H308" s="41"/>
+      <c r="I308" s="41"/>
+      <c r="J308" s="41"/>
+      <c r="K308" s="41"/>
+      <c r="L308" s="69"/>
+      <c r="M308" s="29">
+        <f>M304-M306</f>
+        <v>0</v>
+      </c>
+      <c r="N308" s="29">
+        <f>N304-N306</f>
+        <v>0</v>
+      </c>
+      <c r="O308" s="29">
+        <f>O304-O306</f>
+        <v>0</v>
+      </c>
+      <c r="P308" s="29">
+        <f>P304-P306</f>
+        <v>0</v>
+      </c>
+      <c r="Q308" s="29"/>
+      <c r="R308" s="29">
+        <f>R304-R306</f>
+        <v>0</v>
+      </c>
+      <c r="S308" s="29">
+        <f>S304-S306</f>
+        <v>0</v>
+      </c>
+      <c r="T308" s="29">
+        <f>T304-T306</f>
+        <v>0</v>
+      </c>
+      <c r="U308" s="29">
+        <f>U304-U306</f>
+        <v>0</v>
+      </c>
+      <c r="V308" s="29"/>
+      <c r="W308" s="29">
+        <f>W304-W306</f>
+        <v>0</v>
+      </c>
+      <c r="X308" s="29"/>
+      <c r="Y308" s="56"/>
+      <c r="Z308" s="29"/>
+      <c r="AA308" s="29"/>
+      <c r="AB308" s="29"/>
+      <c r="AC308" s="29"/>
+    </row>
+    <row r="309" spans="1:29">
+      <c r="H309" s="95"/>
+      <c r="I309" s="95"/>
+      <c r="J309" s="95"/>
+      <c r="K309" s="95"/>
+      <c r="M309" s="32"/>
+      <c r="N309" s="32"/>
+      <c r="O309" s="32"/>
+      <c r="P309" s="32"/>
+      <c r="Q309" s="32"/>
+      <c r="R309" s="32"/>
+      <c r="S309" s="32"/>
+      <c r="T309" s="32"/>
+      <c r="U309" s="32"/>
+      <c r="V309" s="32"/>
+      <c r="W309" s="32"/>
+      <c r="X309" s="32"/>
+      <c r="Z309" s="32"/>
+      <c r="AA309" s="32"/>
+      <c r="AB309" s="32"/>
+      <c r="AC309" s="32"/>
+    </row>
+    <row r="310" spans="1:29" s="22" customFormat="1">
+      <c r="A310" s="28"/>
+      <c r="B310" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C311" s="80" t="s">
+      <c r="C310" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D311" s="25" t="s">
+      <c r="D310" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="E311" s="22" t="s">
+      <c r="E310" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="F311" s="22" t="s">
+      <c r="F310" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="G311" s="22" t="s">
+      <c r="G310" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H311" s="41" t="s">
+      <c r="H310" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="I311" s="41"/>
-      <c r="J311" s="41"/>
-      <c r="K311" s="41"/>
-      <c r="L311" s="69"/>
-      <c r="M311" s="41"/>
-      <c r="N311" s="41"/>
-      <c r="O311" s="41"/>
-      <c r="P311" s="41"/>
-      <c r="Q311" s="41"/>
-      <c r="R311" s="41"/>
-      <c r="S311" s="41"/>
-      <c r="T311" s="41"/>
-      <c r="U311" s="41"/>
-      <c r="V311" s="41"/>
-      <c r="W311" s="41"/>
-      <c r="X311" s="41"/>
-      <c r="Y311" s="63"/>
-      <c r="Z311" s="63"/>
-      <c r="AA311" s="41"/>
-      <c r="AB311" s="41"/>
-      <c r="AC311" s="41"/>
+      <c r="I310" s="41"/>
+      <c r="J310" s="41"/>
+      <c r="K310" s="41"/>
+      <c r="L310" s="69"/>
+      <c r="M310" s="41"/>
+      <c r="N310" s="41"/>
+      <c r="O310" s="41"/>
+      <c r="P310" s="41"/>
+      <c r="Q310" s="41"/>
+      <c r="R310" s="41"/>
+      <c r="S310" s="41"/>
+      <c r="T310" s="41"/>
+      <c r="U310" s="41"/>
+      <c r="V310" s="41"/>
+      <c r="W310" s="41"/>
+      <c r="X310" s="41"/>
+      <c r="Y310" s="63"/>
+      <c r="Z310" s="63"/>
+      <c r="AA310" s="41"/>
+      <c r="AB310" s="41"/>
+      <c r="AC310" s="41"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:AD302">
